--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27197BB-4BE6-412F-811E-F46F5828E5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AB4421-28F8-4E78-B155-34E2FB0051DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1164" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="228" windowWidth="23040" windowHeight="12804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="4" r:id="rId1"/>
-    <sheet name="U18_2025" sheetId="6" r:id="rId2"/>
-    <sheet name="U16_2025" sheetId="5" r:id="rId3"/>
-    <sheet name="U16_2024" sheetId="3" r:id="rId4"/>
-    <sheet name="U16_2023" sheetId="2" r:id="rId5"/>
-    <sheet name="U14_2023" sheetId="1" r:id="rId6"/>
+    <sheet name="U18_2026" sheetId="7" r:id="rId2"/>
+    <sheet name="U18_2025" sheetId="6" r:id="rId3"/>
+    <sheet name="U16_2025" sheetId="5" r:id="rId4"/>
+    <sheet name="U16_2024" sheetId="3" r:id="rId5"/>
+    <sheet name="U16_2023" sheetId="2" r:id="rId6"/>
+    <sheet name="U14_2023" sheetId="1" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="172">
   <si>
     <t>sarja</t>
   </si>
@@ -546,6 +547,24 @@
   </si>
   <si>
     <t>tasapeli</t>
+  </si>
+  <si>
+    <t>Katoperä/Setälä</t>
+  </si>
+  <si>
+    <t>Välimäki/Tuunainen</t>
+  </si>
+  <si>
+    <t>18-21,6-21</t>
+  </si>
+  <si>
+    <t>Sieppi/Antola</t>
+  </si>
+  <si>
+    <t>Vilokkinen/Lassila</t>
+  </si>
+  <si>
+    <t>10-21,10-21</t>
   </si>
 </sst>
 </file>
@@ -674,7 +693,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -740,10 +759,9 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -759,7 +777,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1282,16 +1300,43 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
+      <c r="A7" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="10">
+        <v>2026</v>
+      </c>
+      <c r="C7" s="10">
+        <f>SUM(D7:F7)</f>
+        <v>3</v>
+      </c>
+      <c r="D7" s="10">
+        <f>U18_2026!Q2</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <f>U18_2026!S2</f>
+        <v>3</v>
+      </c>
+      <c r="G7" s="10">
+        <f>U18_2026!Q3</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="10">
+        <f>U18_2026!R3</f>
+        <v>9</v>
+      </c>
+      <c r="I7" s="10">
+        <f>U18_2026!Q4</f>
+        <v>78</v>
+      </c>
+      <c r="J7" s="10">
+        <f>U18_2026!R4</f>
+        <v>127</v>
+      </c>
     </row>
     <row r="8" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
@@ -1299,11 +1344,11 @@
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13">
-        <f>SUM(C2:C6)</f>
-        <v>66</v>
+        <f>SUM(C2:C7)</f>
+        <v>69</v>
       </c>
       <c r="D8" s="13">
-        <f t="shared" ref="D8:J8" si="0">SUM(D2:D6)</f>
+        <f t="shared" ref="D8:J8" si="0">SUM(D2:D7)</f>
         <v>23</v>
       </c>
       <c r="E8" s="13">
@@ -1312,7 +1357,7 @@
       </c>
       <c r="F8" s="13">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G8" s="13">
         <f t="shared" si="0"/>
@@ -1320,15 +1365,15 @@
       </c>
       <c r="H8" s="13">
         <f t="shared" si="0"/>
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>2189</v>
+        <v>2267</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>2372</v>
+        <v>2499</v>
       </c>
     </row>
   </sheetData>
@@ -1338,6 +1383,349 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F2E10B0-3E0B-4898-AAC4-7FE75765F048}">
+  <dimension ref="A1:S23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="19" width="10.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="11">
+        <v>3</v>
+      </c>
+      <c r="J1" s="11">
+        <v>2</v>
+      </c>
+      <c r="K1" s="11">
+        <v>1</v>
+      </c>
+      <c r="L1" s="11">
+        <v>0</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="17">
+        <v>46189</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12">
+        <v>34</v>
+      </c>
+      <c r="N2" s="12">
+        <v>43</v>
+      </c>
+      <c r="O2" s="12"/>
+      <c r="P2" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q2" s="12">
+        <f>SUM(I2:I4)</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="12">
+        <f>SUM(L2:L4)</f>
+        <v>3</v>
+      </c>
+      <c r="S2" s="12">
+        <f>SUM(Q2:R2)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="33">
+        <v>46189</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10">
+        <v>1</v>
+      </c>
+      <c r="M3" s="10">
+        <v>20</v>
+      </c>
+      <c r="N3" s="10">
+        <v>42</v>
+      </c>
+      <c r="O3" s="10"/>
+      <c r="P3" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="31">
+        <f>SUM(I3:I21)*3+SUM(J3:J21)</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="31">
+        <f>SUM(K2:K4)*1+SUM(L2:L4)*3</f>
+        <v>9</v>
+      </c>
+      <c r="S3" s="31">
+        <f>SUM(Q3:R3)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="17">
+        <v>46189</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20">
+        <v>1</v>
+      </c>
+      <c r="M4" s="20">
+        <v>24</v>
+      </c>
+      <c r="N4" s="20">
+        <v>42</v>
+      </c>
+      <c r="O4" s="20">
+        <v>9</v>
+      </c>
+      <c r="P4" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q4" s="12">
+        <f>SUM(M2:M4)</f>
+        <v>78</v>
+      </c>
+      <c r="R4" s="12">
+        <f>SUM(N2:N4)</f>
+        <v>127</v>
+      </c>
+      <c r="S4" s="12">
+        <f>SUM(Q4:R4)</f>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B5" s="2"/>
+      <c r="E5" s="3"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B6" s="2"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B7" s="2"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B8" s="2"/>
+      <c r="E8" s="3"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B9" s="2"/>
+      <c r="E9" s="3"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B10" s="2"/>
+      <c r="E10" s="3"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B11" s="2"/>
+      <c r="E11" s="3"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B12" s="2"/>
+      <c r="E12" s="3"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B13" s="9"/>
+      <c r="E13" s="3"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B14" s="9"/>
+      <c r="E14" s="3"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B15" s="9"/>
+      <c r="E15" s="3"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B16" s="9"/>
+      <c r="E16" s="3"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B17" s="9"/>
+      <c r="E17" s="3"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B18" s="9"/>
+      <c r="E18" s="3"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B19" s="9"/>
+      <c r="E19" s="3"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B20" s="9"/>
+      <c r="E20" s="3"/>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <f t="shared" ref="I23:N23" si="0">SUM(I2:I22)</f>
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="0"/>
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5740E14F-6B3B-4441-8DC3-9677609C951F}">
   <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1490,18 +1878,18 @@
         <v>42</v>
       </c>
       <c r="O3" s="10"/>
-      <c r="P3" s="31" t="s">
+      <c r="P3" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="Q3" s="32">
+      <c r="Q3" s="31">
         <f>SUM(I3:I21)*3+SUM(J3:J21)</f>
         <v>0</v>
       </c>
-      <c r="R3" s="32">
+      <c r="R3" s="31">
         <f>SUM(K2:K4)*1+SUM(L2:L4)*3</f>
         <v>9</v>
       </c>
-      <c r="S3" s="32">
+      <c r="S3" s="31">
         <f>SUM(Q3:R3)</f>
         <v>9</v>
       </c>
@@ -1680,12 +2068,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B2117CE-0DBE-45F3-8152-DA2CC07BC64A}">
   <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="19" width="10.77734375" style="28" customWidth="1"/>
+    <col min="1" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -1831,18 +2219,18 @@
       </c>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
-      <c r="P3" s="31" t="s">
+      <c r="P3" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="Q3" s="32">
+      <c r="Q3" s="31">
         <f>3*Q2</f>
         <v>36</v>
       </c>
-      <c r="R3" s="32">
+      <c r="R3" s="31">
         <f>3*R2</f>
         <v>45</v>
       </c>
-      <c r="S3" s="32">
+      <c r="S3" s="31">
         <f>SUM(Q3:R3)</f>
         <v>81</v>
       </c>
@@ -1887,18 +2275,18 @@
         <v>9</v>
       </c>
       <c r="O4" s="12"/>
-      <c r="P4" s="33" t="s">
+      <c r="P4" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="12">
         <f>SUM(L2:L28)</f>
         <v>970</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="12">
         <f>SUM(M2:M28)</f>
         <v>927</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="12">
         <f>SUM(Q4:R4)</f>
         <v>1897</v>
       </c>
@@ -3016,7 +3404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451095BF-90EE-46DB-80DC-AAD7E6F6766E}">
   <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3167,18 +3555,18 @@
       </c>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
-      <c r="P3" s="31" t="s">
+      <c r="P3" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="Q3" s="32">
+      <c r="Q3" s="31">
         <f>Q2*3</f>
         <v>3</v>
       </c>
-      <c r="R3" s="32">
+      <c r="R3" s="31">
         <f>R2*3</f>
         <v>33</v>
       </c>
-      <c r="S3" s="32">
+      <c r="S3" s="31">
         <f>SUM(Q3:R3)</f>
         <v>36</v>
       </c>
@@ -3662,7 +4050,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D22832D-DF07-470D-BD81-86AEA5D4C065}">
   <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3706,7 +4094,7 @@
       <c r="M1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="N1" s="28" t="s">
         <v>146</v>
       </c>
       <c r="O1" s="16"/>
@@ -3817,19 +4205,19 @@
         <v>42</v>
       </c>
       <c r="N3" s="10"/>
-      <c r="O3" s="31" t="s">
+      <c r="O3" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="32">
+      <c r="P3" s="31">
         <f>3*SUM(I2:I13)+SUM(J2:J13)</f>
         <v>5</v>
       </c>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32">
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31">
         <f>SUM(K2:K13)*3+SUM(J2:J13)</f>
         <v>29</v>
       </c>
-      <c r="S3" s="32">
+      <c r="S3" s="31">
         <f>SUM(P3:R3)</f>
         <v>34</v>
       </c>
@@ -4287,7 +4675,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4331,7 +4719,7 @@
       <c r="M1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="N1" s="28" t="s">
         <v>146</v>
       </c>
       <c r="O1" s="11"/>
@@ -4435,18 +4823,18 @@
         <v>42</v>
       </c>
       <c r="N3" s="10"/>
-      <c r="O3" s="31" t="s">
+      <c r="O3" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="32">
+      <c r="P3" s="31">
         <f>SUM(I2:I13)*3</f>
         <v>27</v>
       </c>
-      <c r="Q3" s="32">
+      <c r="Q3" s="31">
         <f>SUM(K2:K13)*3</f>
         <v>9</v>
       </c>
-      <c r="R3" s="32">
+      <c r="R3" s="31">
         <f>SUM(P3:Q3)</f>
         <v>36</v>
       </c>
@@ -4526,7 +4914,7 @@
       <c r="G5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="29" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="10">

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AB4421-28F8-4E78-B155-34E2FB0051DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D393E80C-ED24-466F-A529-647F90B57210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="228" windowWidth="23040" windowHeight="12804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="876" windowWidth="23040" windowHeight="12804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="4" r:id="rId1"/>
-    <sheet name="U18_2026" sheetId="7" r:id="rId2"/>
-    <sheet name="U18_2025" sheetId="6" r:id="rId3"/>
-    <sheet name="U16_2025" sheetId="5" r:id="rId4"/>
-    <sheet name="U16_2024" sheetId="3" r:id="rId5"/>
-    <sheet name="U16_2023" sheetId="2" r:id="rId6"/>
-    <sheet name="U14_2023" sheetId="1" r:id="rId7"/>
+    <sheet name="JNCT_2026" sheetId="8" r:id="rId2"/>
+    <sheet name="U18_2026" sheetId="7" r:id="rId3"/>
+    <sheet name="U18_2025" sheetId="6" r:id="rId4"/>
+    <sheet name="U16_2025" sheetId="5" r:id="rId5"/>
+    <sheet name="U16_2024" sheetId="3" r:id="rId6"/>
+    <sheet name="U16_2023" sheetId="2" r:id="rId7"/>
+    <sheet name="U14_2023" sheetId="1" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="176">
   <si>
     <t>sarja</t>
   </si>
@@ -565,6 +566,18 @@
   </si>
   <si>
     <t>10-21,10-21</t>
+  </si>
+  <si>
+    <t>JNCT</t>
+  </si>
+  <si>
+    <t>Hämeenlinna</t>
+  </si>
+  <si>
+    <t>Rytkönen/Delgado Florez</t>
+  </si>
+  <si>
+    <t>Heikkilä/Wickman</t>
   </si>
 </sst>
 </file>
@@ -717,9 +730,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -778,6 +788,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1060,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF779A0-13B7-4FA6-8975-E321E6508099}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="10.77734375" customWidth="1"/>
@@ -1107,7 +1120,7 @@
         <v>2023</v>
       </c>
       <c r="C2" s="12">
-        <f>SUM(D2:F2)</f>
+        <f t="shared" ref="C2:C8" si="0">SUM(D2:F2)</f>
         <v>12</v>
       </c>
       <c r="D2" s="12">
@@ -1147,7 +1160,7 @@
         <v>2023</v>
       </c>
       <c r="C3" s="10">
-        <f>SUM(D3:F3)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="D3" s="10">
@@ -1187,7 +1200,7 @@
         <v>2024</v>
       </c>
       <c r="C4" s="12">
-        <f>SUM(D4:F4)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="D4" s="12">
@@ -1227,7 +1240,7 @@
         <v>2025</v>
       </c>
       <c r="C5" s="10">
-        <f>SUM(D5:F5)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="D5" s="10">
@@ -1267,7 +1280,7 @@
         <v>2025</v>
       </c>
       <c r="C6" s="12">
-        <f>SUM(D6:F6)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D6" s="12">
@@ -1307,7 +1320,7 @@
         <v>2026</v>
       </c>
       <c r="C7" s="10">
-        <f>SUM(D7:F7)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D7" s="10">
@@ -1338,41 +1351,80 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="12">
+        <v>2026</v>
+      </c>
+      <c r="C8" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="12">
+        <f>JNCT_2026!Q3</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <f>JNCT_2026!S2</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <f>JNCT_2026!Q3</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="12">
+        <f>JNCT_2026!R3</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="12">
+        <f>JNCT_2026!Q4</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="12">
+        <f>JNCT_2026!R4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13">
-        <f>SUM(C2:C7)</f>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33">
+        <f>SUM(C2:C8)</f>
         <v>69</v>
       </c>
-      <c r="D8" s="13">
-        <f t="shared" ref="D8:J8" si="0">SUM(D2:D7)</f>
+      <c r="D9" s="33">
+        <f t="shared" ref="D9:J9" si="1">SUM(D2:D8)</f>
         <v>23</v>
       </c>
-      <c r="E8" s="13">
-        <f t="shared" si="0"/>
+      <c r="E9" s="33">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F8" s="13">
-        <f t="shared" si="0"/>
+      <c r="F9" s="33">
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="G8" s="13">
-        <f t="shared" si="0"/>
+      <c r="G9" s="33">
+        <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="H8" s="13">
-        <f t="shared" si="0"/>
+      <c r="H9" s="33">
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
-      <c r="I8" s="13">
-        <f t="shared" si="0"/>
+      <c r="I9" s="33">
+        <f t="shared" si="1"/>
         <v>2267</v>
       </c>
-      <c r="J8" s="13">
-        <f t="shared" si="0"/>
+      <c r="J9" s="33">
+        <f t="shared" si="1"/>
         <v>2499</v>
       </c>
     </row>
@@ -1383,6 +1435,315 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FAE0EE1-38A3-4036-A726-70F3B327C0F1}">
+  <dimension ref="A1:S23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="19" width="10.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="11">
+        <v>3</v>
+      </c>
+      <c r="J1" s="11">
+        <v>2</v>
+      </c>
+      <c r="K1" s="11">
+        <v>1</v>
+      </c>
+      <c r="L1" s="11">
+        <v>0</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="16">
+        <v>46200</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="G2" s="17"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q2" s="12">
+        <f>SUM(I2:I4)</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="12">
+        <f>SUM(L2:L4)</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="12">
+        <f>SUM(Q2:R2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" s="32">
+        <v>46200</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="G3" s="14"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="30">
+        <f>SUM(I3:I21)*3+SUM(J3:J21)</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="30">
+        <f>SUM(K2:K4)*1+SUM(L2:L4)*3</f>
+        <v>0</v>
+      </c>
+      <c r="S3" s="30">
+        <f>SUM(Q3:R3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="16">
+        <v>46200</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q4" s="12">
+        <f>SUM(M2:M4)</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="12">
+        <f>SUM(N2:N4)</f>
+        <v>0</v>
+      </c>
+      <c r="S4" s="12">
+        <f>SUM(Q4:R4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B5" s="2"/>
+      <c r="E5" s="3"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B6" s="2"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B7" s="2"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B8" s="2"/>
+      <c r="E8" s="3"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B9" s="2"/>
+      <c r="E9" s="3"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B10" s="2"/>
+      <c r="E10" s="3"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B11" s="2"/>
+      <c r="E11" s="3"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B12" s="2"/>
+      <c r="E12" s="3"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B13" s="9"/>
+      <c r="E13" s="3"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B14" s="9"/>
+      <c r="E14" s="3"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B15" s="9"/>
+      <c r="E15" s="3"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B16" s="9"/>
+      <c r="E16" s="3"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B17" s="9"/>
+      <c r="E17" s="3"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B18" s="9"/>
+      <c r="E18" s="3"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B19" s="9"/>
+      <c r="E19" s="3"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B20" s="9"/>
+      <c r="E20" s="3"/>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <f t="shared" ref="I23:N23" si="0">SUM(I2:I22)</f>
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F2E10B0-3E0B-4898-AAC4-7FE75765F048}">
   <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1404,7 +1765,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="11"/>
-      <c r="F1" s="16"/>
+      <c r="F1" s="15"/>
       <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
@@ -1429,10 +1790,10 @@
       <c r="N1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="P1" s="16"/>
+      <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
         <v>144</v>
       </c>
@@ -1447,7 +1808,7 @@
       <c r="A2" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="16">
         <v>46189</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -1462,7 +1823,7 @@
       <c r="F2" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="12" t="s">
@@ -1481,7 +1842,7 @@
         <v>43</v>
       </c>
       <c r="O2" s="12"/>
-      <c r="P2" s="19" t="s">
+      <c r="P2" s="18" t="s">
         <v>164</v>
       </c>
       <c r="Q2" s="12">
@@ -1501,22 +1862,22 @@
       <c r="A3" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3" s="32">
         <v>46189</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="30" t="s">
         <v>166</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="10" t="s">
@@ -1535,27 +1896,27 @@
         <v>42</v>
       </c>
       <c r="O3" s="10"/>
-      <c r="P3" s="30" t="s">
+      <c r="P3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="Q3" s="31">
+      <c r="Q3" s="30">
         <f>SUM(I3:I21)*3+SUM(J3:J21)</f>
         <v>0</v>
       </c>
-      <c r="R3" s="31">
+      <c r="R3" s="30">
         <f>SUM(K2:K4)*1+SUM(L2:L4)*3</f>
         <v>9</v>
       </c>
-      <c r="S3" s="31">
+      <c r="S3" s="30">
         <f>SUM(Q3:R3)</f>
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="16">
         <v>46189</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -1567,31 +1928,31 @@
       <c r="E4" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20">
-        <v>1</v>
-      </c>
-      <c r="M4" s="20">
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19">
+        <v>1</v>
+      </c>
+      <c r="M4" s="19">
         <v>24</v>
       </c>
-      <c r="N4" s="20">
-        <v>42</v>
-      </c>
-      <c r="O4" s="20">
+      <c r="N4" s="19">
+        <v>42</v>
+      </c>
+      <c r="O4" s="19">
         <v>9</v>
       </c>
-      <c r="P4" s="19" t="s">
+      <c r="P4" s="18" t="s">
         <v>79</v>
       </c>
       <c r="Q4" s="12">
@@ -1725,7 +2086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5740E14F-6B3B-4441-8DC3-9677609C951F}">
   <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1747,7 +2108,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="11"/>
-      <c r="F1" s="16"/>
+      <c r="F1" s="15"/>
       <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
@@ -1772,10 +2133,10 @@
       <c r="N1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="P1" s="16"/>
+      <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
         <v>144</v>
       </c>
@@ -1790,7 +2151,7 @@
       <c r="A2" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="16">
         <v>45851</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -1805,7 +2166,7 @@
       <c r="F2" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="12" t="s">
@@ -1824,7 +2185,7 @@
         <v>42</v>
       </c>
       <c r="O2" s="12"/>
-      <c r="P2" s="19" t="s">
+      <c r="P2" s="18" t="s">
         <v>164</v>
       </c>
       <c r="Q2" s="12">
@@ -1844,7 +2205,7 @@
       <c r="A3" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="13">
         <v>45851</v>
       </c>
       <c r="C3" s="10" t="s">
@@ -1859,7 +2220,7 @@
       <c r="F3" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="10" t="s">
@@ -1878,63 +2239,63 @@
         <v>42</v>
       </c>
       <c r="O3" s="10"/>
-      <c r="P3" s="30" t="s">
+      <c r="P3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="Q3" s="31">
+      <c r="Q3" s="30">
         <f>SUM(I3:I21)*3+SUM(J3:J21)</f>
         <v>0</v>
       </c>
-      <c r="R3" s="31">
+      <c r="R3" s="30">
         <f>SUM(K2:K4)*1+SUM(L2:L4)*3</f>
         <v>9</v>
       </c>
-      <c r="S3" s="31">
+      <c r="S3" s="30">
         <f>SUM(Q3:R3)</f>
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="20">
         <v>45851</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="19" t="s">
         <v>62</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20">
-        <v>1</v>
-      </c>
-      <c r="M4" s="20">
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19">
+        <v>1</v>
+      </c>
+      <c r="M4" s="19">
         <v>21</v>
       </c>
-      <c r="N4" s="20">
-        <v>42</v>
-      </c>
-      <c r="O4" s="20">
+      <c r="N4" s="19">
+        <v>42</v>
+      </c>
+      <c r="O4" s="19">
         <v>9</v>
       </c>
-      <c r="P4" s="19" t="s">
+      <c r="P4" s="18" t="s">
         <v>79</v>
       </c>
       <c r="Q4" s="12">
@@ -2068,7 +2429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B2117CE-0DBE-45F3-8152-DA2CC07BC64A}">
   <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2090,7 +2451,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="11"/>
-      <c r="F1" s="16"/>
+      <c r="F1" s="15"/>
       <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
@@ -2115,8 +2476,8 @@
       <c r="N1" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
         <v>143</v>
       </c>
@@ -2131,7 +2492,7 @@
       <c r="A2" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="16">
         <v>45822</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2146,7 +2507,7 @@
       <c r="F2" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>19</v>
       </c>
       <c r="H2" s="12" t="s">
@@ -2165,7 +2526,7 @@
       </c>
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
-      <c r="P2" s="19" t="s">
+      <c r="P2" s="18" t="s">
         <v>164</v>
       </c>
       <c r="Q2" s="12">
@@ -2185,7 +2546,7 @@
       <c r="A3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="13">
         <v>45822</v>
       </c>
       <c r="C3" s="10" t="s">
@@ -2200,7 +2561,7 @@
       <c r="F3" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>35</v>
       </c>
       <c r="H3" s="10" t="s">
@@ -2219,18 +2580,18 @@
       </c>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
-      <c r="P3" s="30" t="s">
+      <c r="P3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="Q3" s="31">
+      <c r="Q3" s="30">
         <f>3*Q2</f>
         <v>36</v>
       </c>
-      <c r="R3" s="31">
+      <c r="R3" s="30">
         <f>3*R2</f>
         <v>45</v>
       </c>
-      <c r="S3" s="31">
+      <c r="S3" s="30">
         <f>SUM(Q3:R3)</f>
         <v>81</v>
       </c>
@@ -2239,7 +2600,7 @@
       <c r="A4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="16">
         <v>45822</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -2254,7 +2615,7 @@
       <c r="F4" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H4" s="12" t="s">
@@ -2275,7 +2636,7 @@
         <v>9</v>
       </c>
       <c r="O4" s="12"/>
-      <c r="P4" s="32" t="s">
+      <c r="P4" s="31" t="s">
         <v>79</v>
       </c>
       <c r="Q4" s="12">
@@ -2295,7 +2656,7 @@
       <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="13">
         <v>45827</v>
       </c>
       <c r="C5" s="10" t="s">
@@ -2310,10 +2671,10 @@
       <c r="F5" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="22" t="s">
         <v>114</v>
       </c>
       <c r="I5" s="10">
@@ -2338,7 +2699,7 @@
       <c r="A6" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="16">
         <v>45827</v>
       </c>
       <c r="C6" s="12" t="s">
@@ -2350,13 +2711,13 @@
       <c r="E6" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="24" t="s">
         <v>116</v>
       </c>
       <c r="I6" s="12"/>
@@ -2381,7 +2742,7 @@
       <c r="A7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>45827</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -2393,13 +2754,13 @@
       <c r="E7" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="22" t="s">
         <v>118</v>
       </c>
       <c r="I7" s="10">
@@ -2424,7 +2785,7 @@
       <c r="A8" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="16">
         <v>45827</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -2439,10 +2800,10 @@
       <c r="F8" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="H8" s="24" t="s">
         <v>120</v>
       </c>
       <c r="I8" s="12"/>
@@ -2467,7 +2828,7 @@
       <c r="A9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="13">
         <v>45837</v>
       </c>
       <c r="C9" s="10" t="s">
@@ -2482,7 +2843,7 @@
       <c r="F9" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="10" t="s">
@@ -2512,7 +2873,7 @@
       <c r="A10" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="16">
         <v>45837</v>
       </c>
       <c r="C10" s="12" t="s">
@@ -2527,7 +2888,7 @@
       <c r="F10" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="17" t="s">
         <v>19</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -2555,7 +2916,7 @@
       <c r="A11" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>45837</v>
       </c>
       <c r="C11" s="10" t="s">
@@ -2570,7 +2931,7 @@
       <c r="F11" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="10" t="s">
@@ -2598,7 +2959,7 @@
       <c r="A12" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="16">
         <v>45837</v>
       </c>
       <c r="C12" s="12" t="s">
@@ -2613,7 +2974,7 @@
       <c r="F12" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -2643,7 +3004,7 @@
       <c r="A13" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="23">
         <v>45839</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -2658,7 +3019,7 @@
       <c r="F13" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H13" s="10" t="s">
@@ -2686,7 +3047,7 @@
       <c r="A14" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="25">
         <v>45839</v>
       </c>
       <c r="C14" s="12" t="s">
@@ -2701,7 +3062,7 @@
       <c r="F14" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H14" s="12" t="s">
@@ -2729,7 +3090,7 @@
       <c r="A15" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="23">
         <v>45839</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -2744,7 +3105,7 @@
       <c r="F15" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H15" s="10" t="s">
@@ -2772,7 +3133,7 @@
       <c r="A16" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="25">
         <v>45839</v>
       </c>
       <c r="C16" s="12" t="s">
@@ -2787,7 +3148,7 @@
       <c r="F16" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H16" s="12" t="s">
@@ -2817,7 +3178,7 @@
       <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="23">
         <v>45844</v>
       </c>
       <c r="C17" s="10" t="s">
@@ -2832,7 +3193,7 @@
       <c r="F17" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H17" s="10" t="s">
@@ -2860,7 +3221,7 @@
       <c r="A18" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="25">
         <v>45844</v>
       </c>
       <c r="C18" s="12" t="s">
@@ -2875,7 +3236,7 @@
       <c r="F18" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H18" s="12" t="s">
@@ -2903,7 +3264,7 @@
       <c r="A19" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="23">
         <v>45844</v>
       </c>
       <c r="C19" s="10" t="s">
@@ -2918,7 +3279,7 @@
       <c r="F19" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H19" s="10" t="s">
@@ -2946,7 +3307,7 @@
       <c r="A20" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="25">
         <v>45844</v>
       </c>
       <c r="C20" s="12" t="s">
@@ -2961,7 +3322,7 @@
       <c r="F20" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="G20" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H20" s="12" t="s">
@@ -2991,7 +3352,7 @@
       <c r="A21" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="23">
         <v>45868</v>
       </c>
       <c r="C21" s="10" t="s">
@@ -3006,7 +3367,7 @@
       <c r="F21" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H21" s="10" t="s">
@@ -3034,7 +3395,7 @@
       <c r="A22" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="25">
         <v>45868</v>
       </c>
       <c r="C22" s="12" t="s">
@@ -3049,7 +3410,7 @@
       <c r="F22" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H22" s="12" t="s">
@@ -3077,7 +3438,7 @@
       <c r="A23" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="23">
         <v>45868</v>
       </c>
       <c r="C23" s="10" t="s">
@@ -3092,7 +3453,7 @@
       <c r="F23" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H23" s="10" t="s">
@@ -3120,7 +3481,7 @@
       <c r="A24" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="25">
         <v>45868</v>
       </c>
       <c r="C24" s="12" t="s">
@@ -3135,7 +3496,7 @@
       <c r="F24" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="17" t="s">
         <v>19</v>
       </c>
       <c r="H24" s="12" t="s">
@@ -3165,7 +3526,7 @@
       <c r="A25" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="23">
         <v>46608</v>
       </c>
       <c r="C25" s="10" t="s">
@@ -3180,7 +3541,7 @@
       <c r="F25" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H25" s="10" t="s">
@@ -3208,7 +3569,7 @@
       <c r="A26" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="25">
         <v>46608</v>
       </c>
       <c r="C26" s="12" t="s">
@@ -3223,7 +3584,7 @@
       <c r="F26" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H26" s="12" t="s">
@@ -3251,7 +3612,7 @@
       <c r="A27" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="23">
         <v>46608</v>
       </c>
       <c r="C27" s="10" t="s">
@@ -3266,7 +3627,7 @@
       <c r="F27" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="G27" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H27" s="10" t="s">
@@ -3294,7 +3655,7 @@
       <c r="A28" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="25">
         <v>46608</v>
       </c>
       <c r="C28" s="12" t="s">
@@ -3309,7 +3670,7 @@
       <c r="F28" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H28" s="12" t="s">
@@ -3336,67 +3697,67 @@
       <c r="S28" s="12"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="26"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="26"/>
+      <c r="S29" s="26"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="27"/>
-      <c r="N30" s="27"/>
-      <c r="O30" s="27"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="26"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="27"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="27"/>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="27"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="26"/>
+      <c r="S31" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3404,7 +3765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451095BF-90EE-46DB-80DC-AAD7E6F6766E}">
   <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3426,7 +3787,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="11"/>
-      <c r="F1" s="16"/>
+      <c r="F1" s="15"/>
       <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
@@ -3451,8 +3812,8 @@
       <c r="N1" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
         <v>80</v>
       </c>
@@ -3467,7 +3828,7 @@
       <c r="A2" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="16">
         <v>45423</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -3482,7 +3843,7 @@
       <c r="F2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="12" t="s">
@@ -3501,7 +3862,7 @@
       </c>
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
-      <c r="P2" s="19" t="s">
+      <c r="P2" s="18" t="s">
         <v>164</v>
       </c>
       <c r="Q2" s="12">
@@ -3521,7 +3882,7 @@
       <c r="A3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="13">
         <v>45423</v>
       </c>
       <c r="C3" s="10" t="s">
@@ -3536,7 +3897,7 @@
       <c r="F3" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="10" t="s">
@@ -3555,18 +3916,18 @@
       </c>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
-      <c r="P3" s="30" t="s">
+      <c r="P3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="Q3" s="31">
+      <c r="Q3" s="30">
         <f>Q2*3</f>
         <v>3</v>
       </c>
-      <c r="R3" s="31">
+      <c r="R3" s="30">
         <f>R2*3</f>
         <v>33</v>
       </c>
-      <c r="S3" s="31">
+      <c r="S3" s="30">
         <f>SUM(Q3:R3)</f>
         <v>36</v>
       </c>
@@ -3575,7 +3936,7 @@
       <c r="A4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="16">
         <v>45423</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -3590,7 +3951,7 @@
       <c r="F4" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H4" s="12" t="s">
@@ -3611,7 +3972,7 @@
         <v>9</v>
       </c>
       <c r="O4" s="12"/>
-      <c r="P4" s="19" t="s">
+      <c r="P4" s="18" t="s">
         <v>79</v>
       </c>
       <c r="Q4" s="12">
@@ -3631,7 +3992,7 @@
       <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="13">
         <v>45458</v>
       </c>
       <c r="C5" s="10" t="s">
@@ -3643,13 +4004,13 @@
       <c r="E5" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="22" t="s">
         <v>91</v>
       </c>
       <c r="I5" s="10"/>
@@ -3674,7 +4035,7 @@
       <c r="A6" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="16">
         <v>45458</v>
       </c>
       <c r="C6" s="12" t="s">
@@ -3686,13 +4047,13 @@
       <c r="E6" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="24" t="s">
         <v>25</v>
       </c>
       <c r="I6" s="12"/>
@@ -3717,7 +4078,7 @@
       <c r="A7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>45458</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -3729,13 +4090,13 @@
       <c r="E7" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="22" t="s">
         <v>94</v>
       </c>
       <c r="I7" s="10"/>
@@ -3760,7 +4121,7 @@
       <c r="A8" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="16">
         <v>45458</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -3775,10 +4136,10 @@
       <c r="F8" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="H8" s="24" t="s">
         <v>95</v>
       </c>
       <c r="I8" s="12"/>
@@ -3805,7 +4166,7 @@
       <c r="A9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <v>45461</v>
       </c>
       <c r="C9" s="10" t="s">
@@ -3820,7 +4181,7 @@
       <c r="F9" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="10" t="s">
@@ -3848,7 +4209,7 @@
       <c r="A10" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="25">
         <v>45461</v>
       </c>
       <c r="C10" s="12" t="s">
@@ -3863,7 +4224,7 @@
       <c r="F10" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -3891,7 +4252,7 @@
       <c r="A11" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="23">
         <v>45461</v>
       </c>
       <c r="C11" s="10" t="s">
@@ -3906,7 +4267,7 @@
       <c r="F11" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="10" t="s">
@@ -3934,7 +4295,7 @@
       <c r="A12" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="25">
         <v>45461</v>
       </c>
       <c r="C12" s="12" t="s">
@@ -3949,7 +4310,7 @@
       <c r="F12" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="17" t="s">
         <v>19</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -3977,7 +4338,7 @@
       <c r="A13" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="23">
         <v>45461</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -3992,7 +4353,7 @@
       <c r="F13" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="10" t="s">
@@ -4050,7 +4411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D22832D-DF07-470D-BD81-86AEA5D4C065}">
   <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4094,10 +4455,10 @@
       <c r="M1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="28" t="s">
+      <c r="N1" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="O1" s="16"/>
+      <c r="O1" s="15"/>
       <c r="P1" s="11" t="s">
         <v>42</v>
       </c>
@@ -4115,7 +4476,7 @@
       <c r="A2" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="16">
         <v>45107</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -4148,7 +4509,7 @@
         <v>42</v>
       </c>
       <c r="N2" s="12"/>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="18" t="s">
         <v>164</v>
       </c>
       <c r="P2" s="12">
@@ -4172,7 +4533,7 @@
       <c r="A3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="13">
         <v>45107</v>
       </c>
       <c r="C3" s="10" t="s">
@@ -4205,19 +4566,19 @@
         <v>42</v>
       </c>
       <c r="N3" s="10"/>
-      <c r="O3" s="30" t="s">
+      <c r="O3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="31">
+      <c r="P3" s="30">
         <f>3*SUM(I2:I13)+SUM(J2:J13)</f>
         <v>5</v>
       </c>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31">
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30">
         <f>SUM(K2:K13)*3+SUM(J2:J13)</f>
         <v>29</v>
       </c>
-      <c r="S3" s="31">
+      <c r="S3" s="30">
         <f>SUM(P3:R3)</f>
         <v>34</v>
       </c>
@@ -4226,7 +4587,7 @@
       <c r="A4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="16">
         <v>45107</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -4241,7 +4602,7 @@
       <c r="F4" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="17" t="s">
         <v>46</v>
       </c>
       <c r="H4" s="12" t="s">
@@ -4259,7 +4620,7 @@
         <v>35</v>
       </c>
       <c r="N4" s="12"/>
-      <c r="O4" s="19" t="s">
+      <c r="O4" s="18" t="s">
         <v>79</v>
       </c>
       <c r="P4" s="12">
@@ -4280,7 +4641,7 @@
       <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="13">
         <v>45107</v>
       </c>
       <c r="C5" s="10" t="s">
@@ -4295,7 +4656,7 @@
       <c r="F5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>46</v>
       </c>
       <c r="H5" s="10" t="s">
@@ -4323,7 +4684,7 @@
       <c r="A6" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="16">
         <v>45107</v>
       </c>
       <c r="C6" s="12" t="s">
@@ -4338,7 +4699,7 @@
       <c r="F6" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="17" t="s">
         <v>35</v>
       </c>
       <c r="H6" s="12" t="s">
@@ -4368,7 +4729,7 @@
       <c r="A7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>45112</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -4383,7 +4744,7 @@
       <c r="F7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="10" t="s">
@@ -4411,7 +4772,7 @@
       <c r="A8" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="16">
         <v>45112</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -4426,10 +4787,10 @@
       <c r="F8" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="17" t="s">
         <v>56</v>
       </c>
       <c r="I8" s="12"/>
@@ -4454,7 +4815,7 @@
       <c r="A9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="13">
         <v>45112</v>
       </c>
       <c r="C9" s="10" t="s">
@@ -4469,7 +4830,7 @@
       <c r="F9" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H9" s="10" t="s">
@@ -4497,7 +4858,7 @@
       <c r="A10" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="16">
         <v>45112</v>
       </c>
       <c r="C10" s="12" t="s">
@@ -4512,7 +4873,7 @@
       <c r="F10" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -4542,7 +4903,7 @@
       <c r="A11" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>45122</v>
       </c>
       <c r="C11" s="10" t="s">
@@ -4554,10 +4915,10 @@
       <c r="E11" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="10" t="s">
@@ -4585,7 +4946,7 @@
       <c r="A12" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="16">
         <v>45122</v>
       </c>
       <c r="C12" s="12" t="s">
@@ -4597,10 +4958,10 @@
       <c r="E12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -4625,10 +4986,10 @@
       <c r="S12" s="12"/>
     </row>
     <row r="13" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>45122</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -4640,10 +5001,10 @@
       <c r="E13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="10" t="s">
@@ -4675,7 +5036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4719,7 +5080,7 @@
       <c r="M1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="28" t="s">
+      <c r="N1" s="27" t="s">
         <v>146</v>
       </c>
       <c r="O1" s="11"/>
@@ -4737,7 +5098,7 @@
       <c r="A2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="16">
         <v>45091</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -4752,7 +5113,7 @@
       <c r="F2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="12" t="s">
@@ -4770,7 +5131,7 @@
         <v>50</v>
       </c>
       <c r="N2" s="12"/>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="18" t="s">
         <v>164</v>
       </c>
       <c r="P2" s="12">
@@ -4790,7 +5151,7 @@
       <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="13">
         <v>45091</v>
       </c>
       <c r="C3" s="10" t="s">
@@ -4823,18 +5184,18 @@
         <v>42</v>
       </c>
       <c r="N3" s="10"/>
-      <c r="O3" s="30" t="s">
+      <c r="O3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="31">
+      <c r="P3" s="30">
         <f>SUM(I2:I13)*3</f>
         <v>27</v>
       </c>
-      <c r="Q3" s="31">
+      <c r="Q3" s="30">
         <f>SUM(K2:K13)*3</f>
         <v>9</v>
       </c>
-      <c r="R3" s="31">
+      <c r="R3" s="30">
         <f>SUM(P3:Q3)</f>
         <v>36</v>
       </c>
@@ -4843,7 +5204,7 @@
       <c r="A4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="16">
         <v>45091</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -4876,7 +5237,7 @@
         <v>9</v>
       </c>
       <c r="N4" s="12"/>
-      <c r="O4" s="19" t="s">
+      <c r="O4" s="18" t="s">
         <v>79</v>
       </c>
       <c r="P4" s="12">
@@ -4896,7 +5257,7 @@
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="13">
         <v>45091</v>
       </c>
       <c r="C5" s="10" t="s">
@@ -4914,7 +5275,7 @@
       <c r="G5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="28" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="10">
@@ -4938,7 +5299,7 @@
       <c r="A6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="16">
         <v>45091</v>
       </c>
       <c r="C6" s="12" t="s">
@@ -4953,7 +5314,7 @@
       <c r="F6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="17" t="s">
         <v>13</v>
       </c>
       <c r="H6" s="12" t="s">
@@ -4980,7 +5341,7 @@
       <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>45091</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -5024,7 +5385,7 @@
       <c r="A8" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="16">
         <v>45095</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -5066,7 +5427,7 @@
       <c r="A9" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="13">
         <v>45095</v>
       </c>
       <c r="C9" s="10" t="s">
@@ -5108,7 +5469,7 @@
       <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="16">
         <v>45095</v>
       </c>
       <c r="C10" s="12" t="s">
@@ -5150,7 +5511,7 @@
       <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>45095</v>
       </c>
       <c r="C11" s="10" t="s">
@@ -5192,7 +5553,7 @@
       <c r="A12" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="16">
         <v>45095</v>
       </c>
       <c r="C12" s="12" t="s">
@@ -5234,7 +5595,7 @@
       <c r="A13" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>45095</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -5249,7 +5610,7 @@
       <c r="F13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="14" t="s">
         <v>35</v>
       </c>
       <c r="H13" s="10" t="s">

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D393E80C-ED24-466F-A529-647F90B57210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D2DB93-00A8-437F-A424-EA12CF8AEC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="876" windowWidth="23040" windowHeight="12804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="180">
   <si>
     <t>sarja</t>
   </si>
@@ -578,6 +578,18 @@
   </si>
   <si>
     <t>Heikkilä/Wickman</t>
+  </si>
+  <si>
+    <t>Seppänen/Mäkinen</t>
+  </si>
+  <si>
+    <t>13-21,15-21</t>
+  </si>
+  <si>
+    <t>15-21,11-21</t>
+  </si>
+  <si>
+    <t>11-21,14-21</t>
   </si>
 </sst>
 </file>
@@ -1360,7 +1372,7 @@
       </c>
       <c r="C8" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" s="12">
         <f>JNCT_2026!Q3</f>
@@ -1371,7 +1383,7 @@
       </c>
       <c r="F8" s="12">
         <f>JNCT_2026!S2</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" s="12">
         <f>JNCT_2026!Q3</f>
@@ -1379,15 +1391,15 @@
       </c>
       <c r="H8" s="12">
         <f>JNCT_2026!R3</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I8" s="12">
         <f>JNCT_2026!Q4</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J8" s="12">
         <f>JNCT_2026!R4</f>
-        <v>0</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1397,7 +1409,7 @@
       <c r="B9" s="33"/>
       <c r="C9" s="33">
         <f>SUM(C2:C8)</f>
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D9" s="33">
         <f t="shared" ref="D9:J9" si="1">SUM(D2:D8)</f>
@@ -1409,7 +1421,7 @@
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G9" s="33">
         <f t="shared" si="1"/>
@@ -1417,15 +1429,15 @@
       </c>
       <c r="H9" s="33">
         <f t="shared" si="1"/>
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I9" s="33">
         <f t="shared" si="1"/>
-        <v>2267</v>
+        <v>2346</v>
       </c>
       <c r="J9" s="33">
         <f t="shared" si="1"/>
-        <v>2499</v>
+        <v>2625</v>
       </c>
     </row>
   </sheetData>
@@ -1514,14 +1526,24 @@
       <c r="F2" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="12"/>
+      <c r="G2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>179</v>
+      </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
       <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
+      <c r="L2" s="12">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12">
+        <v>25</v>
+      </c>
+      <c r="N2" s="12">
+        <v>42</v>
+      </c>
       <c r="O2" s="12"/>
       <c r="P2" s="18" t="s">
         <v>164</v>
@@ -1532,11 +1554,11 @@
       </c>
       <c r="R2" s="12">
         <f>SUM(L2:L4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S2" s="12">
         <f>SUM(Q2:R2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1558,14 +1580,24 @@
       <c r="F3" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="10"/>
+      <c r="G3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>178</v>
+      </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="L3" s="10">
+        <v>1</v>
+      </c>
+      <c r="M3" s="10">
+        <v>26</v>
+      </c>
+      <c r="N3" s="10">
+        <v>42</v>
+      </c>
       <c r="O3" s="10"/>
       <c r="P3" s="29" t="s">
         <v>7</v>
@@ -1576,11 +1608,11 @@
       </c>
       <c r="R3" s="30">
         <f>SUM(K2:K4)*1+SUM(L2:L4)*3</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S3" s="30">
         <f>SUM(Q3:R3)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1599,30 +1631,42 @@
       <c r="E4" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="19"/>
+      <c r="F4" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>177</v>
+      </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
       <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="L4" s="19">
+        <v>1</v>
+      </c>
+      <c r="M4" s="19">
+        <v>28</v>
+      </c>
+      <c r="N4" s="19">
+        <v>42</v>
+      </c>
       <c r="O4" s="19"/>
       <c r="P4" s="18" t="s">
         <v>79</v>
       </c>
       <c r="Q4" s="12">
         <f>SUM(M2:M4)</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="R4" s="12">
         <f>SUM(N2:N4)</f>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="S4" s="12">
         <f>SUM(Q4:R4)</f>
-        <v>0</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -1726,15 +1770,15 @@
       </c>
       <c r="L23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="N23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D2DB93-00A8-437F-A424-EA12CF8AEC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F13432E2-4ADE-464E-B5A3-62B0161B0917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="876" windowWidth="23040" windowHeight="12804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="197">
   <si>
     <t>sarja</t>
   </si>
@@ -590,6 +590,58 @@
   </si>
   <si>
     <t>11-21,14-21</t>
+  </si>
+  <si>
+    <t>Ma</t>
+  </si>
+  <si>
+    <t>Katoperä/Errkonen</t>
+  </si>
+  <si>
+    <t>Antola/Sieppi</t>
+  </si>
+  <si>
+    <t>Lindell/Heimonen</t>
+  </si>
+  <si>
+    <t>Strang/Päivärinta</t>
+  </si>
+  <si>
+    <t>Tihinen/Louhimaa</t>
+  </si>
+  <si>
+    <t>14-21,21-12</t>
+  </si>
+  <si>
+    <t>24-22,21-15</t>
+  </si>
+  <si>
+    <t>10-21,8-21</t>
+  </si>
+  <si>
+    <t>21-19,21-14</t>
+  </si>
+  <si>
+    <t>Katoperä/Setälä/Erkkonen</t>
+  </si>
+  <si>
+    <t>Katoperä/
+Antola</t>
+  </si>
+  <si>
+    <t>Katoperä/Erkkonen</t>
+  </si>
+  <si>
+    <t>28-26,21-14</t>
+  </si>
+  <si>
+    <t>12-21,17-21</t>
+  </si>
+  <si>
+    <t>Niskasaari/Tihinen</t>
+  </si>
+  <si>
+    <t>20-22,18-21</t>
   </si>
 </sst>
 </file>
@@ -718,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -804,6 +856,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1333,33 +1397,34 @@
       </c>
       <c r="C7" s="10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D7" s="10">
         <f>U18_2026!Q2</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="10">
-        <v>0</v>
+        <f>U18_2026!R2</f>
+        <v>1</v>
       </c>
       <c r="F7" s="10">
-        <f>U18_2026!S2</f>
-        <v>3</v>
+        <f>U18_2026!T2</f>
+        <v>10</v>
       </c>
       <c r="G7" s="10">
         <f>U18_2026!Q3</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H7" s="10">
-        <f>U18_2026!R3</f>
-        <v>9</v>
+        <f>U18_2026!S3</f>
+        <v>19</v>
       </c>
       <c r="I7" s="10">
         <f>U18_2026!Q4</f>
         <v>78</v>
       </c>
       <c r="J7" s="10">
-        <f>U18_2026!R4</f>
+        <f>U18_2026!S4</f>
         <v>127</v>
       </c>
     </row>
@@ -1409,27 +1474,27 @@
       <c r="B9" s="33"/>
       <c r="C9" s="33">
         <f>SUM(C2:C8)</f>
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D9" s="33">
         <f t="shared" ref="D9:J9" si="1">SUM(D2:D8)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E9" s="33">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G9" s="33">
         <f t="shared" si="1"/>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H9" s="33">
         <f t="shared" si="1"/>
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="I9" s="33">
         <f t="shared" si="1"/>
@@ -1498,7 +1563,7 @@
       </c>
       <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="R1" s="11" t="s">
         <v>77</v>
@@ -1789,7 +1854,689 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F2E10B0-3E0B-4898-AAC4-7FE75765F048}">
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="20" width="10.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="11">
+        <v>3</v>
+      </c>
+      <c r="J1" s="11">
+        <v>2</v>
+      </c>
+      <c r="K1" s="11">
+        <v>1</v>
+      </c>
+      <c r="L1" s="11">
+        <v>0</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="16">
+        <v>46189</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12">
+        <v>34</v>
+      </c>
+      <c r="N2" s="12">
+        <v>43</v>
+      </c>
+      <c r="O2" s="12"/>
+      <c r="P2" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q2" s="12">
+        <f>SUM(I2:I20)+SUM(J2:J20)</f>
+        <v>3</v>
+      </c>
+      <c r="R2" s="12">
+        <f>SUM(K2:K20)</f>
+        <v>1</v>
+      </c>
+      <c r="S2" s="12">
+        <f>SUM(L2:L20)</f>
+        <v>6</v>
+      </c>
+      <c r="T2" s="12">
+        <f t="shared" ref="T2:T9" si="0">SUM(Q2:S2)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="32">
+        <v>46189</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10">
+        <v>1</v>
+      </c>
+      <c r="M3" s="10">
+        <v>20</v>
+      </c>
+      <c r="N3" s="10">
+        <v>42</v>
+      </c>
+      <c r="O3" s="10"/>
+      <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="30">
+        <f>SUM(I2:I20)*3+SUM(J2:J20)*2+SUM(K2:K20)</f>
+        <v>8</v>
+      </c>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30">
+        <f>SUM(K2:K20)*1+SUM(L2:L20)*3</f>
+        <v>19</v>
+      </c>
+      <c r="T3" s="30">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="16">
+        <v>46189</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19">
+        <v>1</v>
+      </c>
+      <c r="M4" s="19">
+        <v>24</v>
+      </c>
+      <c r="N4" s="19">
+        <v>42</v>
+      </c>
+      <c r="O4" s="19">
+        <v>9</v>
+      </c>
+      <c r="P4" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q4" s="12">
+        <f>SUM(M2:M4)</f>
+        <v>78</v>
+      </c>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12">
+        <f>SUM(N2:N4)</f>
+        <v>127</v>
+      </c>
+      <c r="T4" s="12">
+        <f t="shared" si="0"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="32">
+        <v>46202</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30">
+        <v>1</v>
+      </c>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30">
+        <v>35</v>
+      </c>
+      <c r="N5" s="30">
+        <v>33</v>
+      </c>
+      <c r="O5" s="30"/>
+      <c r="P5" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q5" s="30">
+        <f>SUM(I5:I7)</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30">
+        <f>SUM(L5:L7)</f>
+        <v>1</v>
+      </c>
+      <c r="T5" s="30">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="16">
+        <v>46202</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12">
+        <v>1</v>
+      </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12">
+        <v>45</v>
+      </c>
+      <c r="N6" s="12">
+        <v>37</v>
+      </c>
+      <c r="O6" s="12"/>
+      <c r="P6" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q6" s="12">
+        <f>SUM(I6:I24)*3+SUM(J6:J24)</f>
+        <v>5</v>
+      </c>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12">
+        <f>SUM(K5:K7)*1+SUM(L5:L7)*3</f>
+        <v>4</v>
+      </c>
+      <c r="T6" s="12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="32">
+        <v>46202</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35">
+        <v>1</v>
+      </c>
+      <c r="M7" s="35">
+        <v>18</v>
+      </c>
+      <c r="N7" s="35">
+        <v>42</v>
+      </c>
+      <c r="O7" s="35"/>
+      <c r="P7" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q7" s="30">
+        <f>SUM(M5:M7)</f>
+        <v>98</v>
+      </c>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30">
+        <f>SUM(N5:N7)</f>
+        <v>112</v>
+      </c>
+      <c r="T7" s="30">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="16">
+        <v>46202</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12">
+        <v>1</v>
+      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12">
+        <v>42</v>
+      </c>
+      <c r="N8" s="12">
+        <v>33</v>
+      </c>
+      <c r="O8" s="12"/>
+      <c r="P8" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q8" s="12">
+        <f>SUM(I8:I26)*3+SUM(J8:J26)</f>
+        <v>4</v>
+      </c>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12">
+        <f>SUM(K7:K9)*1+SUM(L7:L9)*3</f>
+        <v>3</v>
+      </c>
+      <c r="T8" s="12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="32">
+        <v>46202</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="I9" s="35">
+        <v>1</v>
+      </c>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35">
+        <v>49</v>
+      </c>
+      <c r="N9" s="35">
+        <v>40</v>
+      </c>
+      <c r="O9" s="35"/>
+      <c r="P9" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q9" s="30">
+        <f>SUM(M7:M9)</f>
+        <v>109</v>
+      </c>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30">
+        <f>SUM(N7:N9)</f>
+        <v>115</v>
+      </c>
+      <c r="T9" s="30">
+        <f t="shared" si="0"/>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" s="16">
+        <v>46202</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12">
+        <v>1</v>
+      </c>
+      <c r="M10" s="12">
+        <v>29</v>
+      </c>
+      <c r="N10" s="12">
+        <v>42</v>
+      </c>
+      <c r="O10" s="12"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+    </row>
+    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="32">
+        <v>46202</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="G11" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35">
+        <v>1</v>
+      </c>
+      <c r="M11" s="35">
+        <v>38</v>
+      </c>
+      <c r="N11" s="35">
+        <v>43</v>
+      </c>
+      <c r="O11" s="35"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="32"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B14" s="9"/>
+      <c r="E14" s="3"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B15" s="9"/>
+      <c r="E15" s="3"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B16" s="9"/>
+      <c r="E16" s="3"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="9"/>
+      <c r="E17" s="3"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="9"/>
+      <c r="E18" s="3"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="9"/>
+      <c r="E19" s="3"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="9"/>
+      <c r="E20" s="3"/>
+      <c r="G20" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5740E14F-6B3B-4441-8DC3-9677609C951F}">
+  <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="19" width="10.77734375" customWidth="1"/>
@@ -1853,25 +2600,25 @@
         <v>142</v>
       </c>
       <c r="B2" s="16">
-        <v>46189</v>
+        <v>45851</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="G2" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -1883,7 +2630,7 @@
         <v>34</v>
       </c>
       <c r="N2" s="12">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="18" t="s">
@@ -1906,26 +2653,26 @@
       <c r="A3" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B3" s="32">
-        <v>46189</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="30" t="s">
-        <v>166</v>
+      <c r="B3" s="13">
+        <v>45851</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>145</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -1934,7 +2681,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N3" s="10">
         <v>42</v>
@@ -1960,26 +2707,26 @@
       <c r="A4" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="B4" s="16">
-        <v>46189</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>10</v>
+      <c r="B4" s="20">
+        <v>45851</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="G4" s="21" t="s">
         <v>16</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -1988,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="M4" s="19">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N4" s="19">
         <v>42</v>
@@ -2001,15 +2748,15 @@
       </c>
       <c r="Q4" s="12">
         <f>SUM(M2:M4)</f>
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="R4" s="12">
         <f>SUM(N2:N4)</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S4" s="12">
         <f>SUM(Q4:R4)</f>
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -2078,394 +2825,25 @@
       <c r="E16" s="3"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="9"/>
       <c r="E17" s="3"/>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="9"/>
       <c r="E18" s="3"/>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="9"/>
       <c r="E19" s="3"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="9"/>
       <c r="E20" s="3"/>
       <c r="G20" s="4"/>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="I23">
-        <f t="shared" ref="I23:N23" si="0">SUM(I2:I22)</f>
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="0"/>
-        <v>78</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="0"/>
-        <v>127</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5740E14F-6B3B-4441-8DC3-9677609C951F}">
-  <dimension ref="A1:S23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="19" width="10.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="11">
-        <v>3</v>
-      </c>
-      <c r="J1" s="11">
-        <v>2</v>
-      </c>
-      <c r="K1" s="11">
-        <v>1</v>
-      </c>
-      <c r="L1" s="11">
-        <v>0</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="S1" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="16">
-        <v>45851</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12">
-        <v>1</v>
-      </c>
-      <c r="M2" s="12">
-        <v>34</v>
-      </c>
-      <c r="N2" s="12">
-        <v>42</v>
-      </c>
-      <c r="O2" s="12"/>
-      <c r="P2" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q2" s="12">
-        <f>SUM(I2:I4)</f>
-        <v>0</v>
-      </c>
-      <c r="R2" s="12">
-        <f>SUM(L2:L4)</f>
-        <v>3</v>
-      </c>
-      <c r="S2" s="12">
-        <f>SUM(Q2:R2)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B3" s="13">
-        <v>45851</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10">
-        <v>1</v>
-      </c>
-      <c r="M3" s="10">
-        <v>17</v>
-      </c>
-      <c r="N3" s="10">
-        <v>42</v>
-      </c>
-      <c r="O3" s="10"/>
-      <c r="P3" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q3" s="30">
-        <f>SUM(I3:I21)*3+SUM(J3:J21)</f>
-        <v>0</v>
-      </c>
-      <c r="R3" s="30">
-        <f>SUM(K2:K4)*1+SUM(L2:L4)*3</f>
-        <v>9</v>
-      </c>
-      <c r="S3" s="30">
-        <f>SUM(Q3:R3)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="20">
-        <v>45851</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19">
-        <v>1</v>
-      </c>
-      <c r="M4" s="19">
-        <v>21</v>
-      </c>
-      <c r="N4" s="19">
-        <v>42</v>
-      </c>
-      <c r="O4" s="19">
-        <v>9</v>
-      </c>
-      <c r="P4" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q4" s="12">
-        <f>SUM(M2:M4)</f>
-        <v>72</v>
-      </c>
-      <c r="R4" s="12">
-        <f>SUM(N2:N4)</f>
-        <v>126</v>
-      </c>
-      <c r="S4" s="12">
-        <f>SUM(Q4:R4)</f>
-        <v>198</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B5" s="2"/>
-      <c r="E5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B6" s="2"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B7" s="2"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B8" s="2"/>
-      <c r="E8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B9" s="2"/>
-      <c r="E9" s="3"/>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="2"/>
-      <c r="E10" s="3"/>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="2"/>
-      <c r="E11" s="3"/>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B12" s="2"/>
-      <c r="E12" s="3"/>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B13" s="9"/>
-      <c r="E13" s="3"/>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="9"/>
-      <c r="E14" s="3"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="9"/>
-      <c r="E15" s="3"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="9"/>
-      <c r="E16" s="3"/>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B17" s="9"/>
-      <c r="E17" s="3"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B18" s="9"/>
-      <c r="E18" s="3"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B19" s="9"/>
-      <c r="E19" s="3"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B20" s="9"/>
-      <c r="E20" s="3"/>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="I23">
-        <f t="shared" ref="I23:N23" si="0">SUM(I2:I22)</f>
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="0"/>
-        <v>126</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3811,7 +4189,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451095BF-90EE-46DB-80DC-AAD7E6F6766E}">
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="19" width="10.77734375" customWidth="1"/>
@@ -4426,28 +4804,6 @@
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B14" s="9"/>
       <c r="E14" s="3"/>
-    </row>
-    <row r="23" spans="9:13" x14ac:dyDescent="0.3">
-      <c r="I23">
-        <f>SUM(I2:I22)</f>
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <f>SUM(J2:J22)</f>
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <f>SUM(K2:K22)</f>
-        <v>11</v>
-      </c>
-      <c r="L23">
-        <f>SUM(L2:L22)</f>
-        <v>344</v>
-      </c>
-      <c r="M23">
-        <f>SUM(M2:M22)</f>
-        <v>509</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F13432E2-4ADE-464E-B5A3-62B0161B0917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8B38F4-D539-412A-A06E-4E13D667B948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2442,7 +2442,9 @@
       <c r="N11" s="35">
         <v>43</v>
       </c>
-      <c r="O11" s="35"/>
+      <c r="O11" s="35">
+        <v>4</v>
+      </c>
       <c r="P11" s="29"/>
       <c r="Q11" s="30"/>
       <c r="R11" s="30"/>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8B38F4-D539-412A-A06E-4E13D667B948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9DFDA4-81C5-4A3E-9736-E7A88FDB7E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="196">
   <si>
     <t>sarja</t>
   </si>
@@ -92,33 +92,21 @@
     <t>21-18,18-21,15-11</t>
   </si>
   <si>
-    <t>Esko/Kerman</t>
-  </si>
-  <si>
     <t>0-2</t>
   </si>
   <si>
     <t>13-21,18-21</t>
   </si>
   <si>
-    <t>Kuusipalo/Isid</t>
-  </si>
-  <si>
     <t>2-0</t>
   </si>
   <si>
     <t>21-5,21-4</t>
   </si>
   <si>
-    <t>Mattila/Laurila</t>
-  </si>
-  <si>
     <t>21-12,21-8</t>
   </si>
   <si>
-    <t>Vesanen/Rainio</t>
-  </si>
-  <si>
     <t>17-21,21-19,15-10</t>
   </si>
   <si>
@@ -131,9 +119,6 @@
     <t>Eura</t>
   </si>
   <si>
-    <t>Laukkanen/Sieppi</t>
-  </si>
-  <si>
     <t>21-3,21-11</t>
   </si>
   <si>
@@ -141,9 +126,6 @@
   </si>
   <si>
     <t>21-18,21-14</t>
-  </si>
-  <si>
-    <t>Virkunen/Schreibmaier</t>
   </si>
   <si>
     <t>21-7,21-2</t>
@@ -213,21 +195,12 @@
     <t>12-21,9-21</t>
   </si>
   <si>
-    <t>Marttila/Välimäki</t>
-  </si>
-  <si>
     <t>10-21,5-21</t>
   </si>
   <si>
-    <t>Salmi/Lietsala</t>
-  </si>
-  <si>
     <t>21-14,21-19</t>
   </si>
   <si>
-    <t>Nevala/Virtanen</t>
-  </si>
-  <si>
     <t>17-21,12-21</t>
   </si>
   <si>
@@ -237,37 +210,19 @@
     <t>Vaasa</t>
   </si>
   <si>
-    <t>Ahonen/Järvi-Laturi</t>
-  </si>
-  <si>
     <t>4-21,10-21</t>
   </si>
   <si>
-    <t>Välimäki/Roininen</t>
-  </si>
-  <si>
     <t>7-21,14-21</t>
   </si>
   <si>
-    <t>Kuokkanen/Hiitti</t>
-  </si>
-  <si>
     <t>10-21,13-21</t>
   </si>
   <si>
     <t>Vantaa</t>
   </si>
   <si>
-    <t>Katoperä/Sieppi</t>
-  </si>
-  <si>
-    <t>Mattila/Talvia</t>
-  </si>
-  <si>
     <t>15-21,16-21</t>
-  </si>
-  <si>
-    <t>Oivanen/Holm</t>
   </si>
   <si>
     <t>8-21,13-21</t>
@@ -320,18 +275,9 @@
     <t>eräpisteet muut</t>
   </si>
   <si>
-    <t>Pöyhönen/Peltonen</t>
-  </si>
-  <si>
     <t>15-21,18-21</t>
   </si>
   <si>
-    <t>Kerman/Nykänen</t>
-  </si>
-  <si>
-    <t>Nieminen/Rapeli</t>
-  </si>
-  <si>
     <t>21-18,17-21,12-15</t>
   </si>
   <si>
@@ -341,75 +287,45 @@
     <t>Ti</t>
   </si>
   <si>
-    <t>Riponiemi/Laine</t>
-  </si>
-  <si>
     <t>17-21,14-21</t>
   </si>
   <si>
-    <t>Heimala/Peltonen</t>
-  </si>
-  <si>
     <t>11-21,21-23</t>
   </si>
   <si>
-    <t>Huhta/Kumpulainen</t>
-  </si>
-  <si>
     <t>4-21,8-21</t>
   </si>
   <si>
     <t>22-20,21-15</t>
   </si>
   <si>
-    <t>Rainio/Vesanen</t>
-  </si>
-  <si>
     <t>14-21,15-21</t>
   </si>
   <si>
     <t>Katoperä/Paloniemi</t>
   </si>
   <si>
-    <t>Luoto/Hakamäki</t>
-  </si>
-  <si>
     <t>21-6,21,3</t>
   </si>
   <si>
     <t>18-21,21-17,13-15</t>
   </si>
   <si>
-    <t>Oivanen/Nurminen</t>
-  </si>
-  <si>
     <t>14-21, 17-21</t>
   </si>
   <si>
     <t>To</t>
   </si>
   <si>
-    <t>Temisevä/Ylitalo</t>
-  </si>
-  <si>
     <t>21-3,21-6</t>
   </si>
   <si>
-    <t>Rainio/Välimäki</t>
-  </si>
-  <si>
     <t>17-21,18-21</t>
   </si>
   <si>
-    <t>Jokinen/Mäenpää</t>
-  </si>
-  <si>
     <t>21-13,21-13</t>
   </si>
   <si>
-    <t>Peltonen/Parkkisenniemi</t>
-  </si>
-  <si>
     <t>8-21,15-21</t>
   </si>
   <si>
@@ -422,33 +338,15 @@
     <t>15-21,14-21</t>
   </si>
   <si>
-    <t>Hakala/Peippo</t>
-  </si>
-  <si>
     <t>21-10,21-16</t>
   </si>
   <si>
-    <t>Rajala/Tuunainen</t>
-  </si>
-  <si>
     <t>21-18,28-26</t>
   </si>
   <si>
-    <t>Heimala/Lehiö</t>
-  </si>
-  <si>
     <t>16-21,20-22</t>
   </si>
   <si>
-    <t>Katoperä/Antola</t>
-  </si>
-  <si>
-    <t>Välimäki/Vuorentausta</t>
-  </si>
-  <si>
-    <t>Antikainen/Puttonen</t>
-  </si>
-  <si>
     <t>21-14,21-13</t>
   </si>
   <si>
@@ -456,15 +354,6 @@
   </si>
   <si>
     <t>21-16,21-16</t>
-  </si>
-  <si>
-    <t>Sieppi/Syri</t>
-  </si>
-  <si>
-    <t>Nurmi/Keränen</t>
-  </si>
-  <si>
-    <t>Kerman/Peltonen</t>
   </si>
   <si>
     <t>21-12,21-9</t>
@@ -487,27 +376,15 @@
 Katoperä</t>
   </si>
   <si>
-    <t>Katoperä/Katoperä</t>
-  </si>
-  <si>
     <t>sijoitus</t>
   </si>
   <si>
-    <t>Piispanen/Vilokkinen</t>
-  </si>
-  <si>
     <t>17-21,17-21</t>
   </si>
   <si>
-    <t>Ruuska/Nauha</t>
-  </si>
-  <si>
     <t>7-21,10-21</t>
   </si>
   <si>
-    <t>Heikkilä/Kaustinen</t>
-  </si>
-  <si>
     <t>10-21,11-21</t>
   </si>
   <si>
@@ -517,9 +394,6 @@
     <t>Antila/Tuunainen</t>
   </si>
   <si>
-    <t>Rapeli/Vilenius</t>
-  </si>
-  <si>
     <t>12-21,18-21</t>
   </si>
   <si>
@@ -532,39 +406,18 @@
     <t>21-18.21-19</t>
   </si>
   <si>
-    <t>Heimala/Kerman</t>
-  </si>
-  <si>
-    <t>Hakamäki/Luoto</t>
-  </si>
-  <si>
     <t>21-4,21-8</t>
   </si>
   <si>
-    <t>Peippo/Uusitalo</t>
-  </si>
-  <si>
     <t>voitot</t>
   </si>
   <si>
     <t>tasapeli</t>
   </si>
   <si>
-    <t>Katoperä/Setälä</t>
-  </si>
-  <si>
-    <t>Välimäki/Tuunainen</t>
-  </si>
-  <si>
     <t>18-21,6-21</t>
   </si>
   <si>
-    <t>Sieppi/Antola</t>
-  </si>
-  <si>
-    <t>Vilokkinen/Lassila</t>
-  </si>
-  <si>
     <t>10-21,10-21</t>
   </si>
   <si>
@@ -574,15 +427,6 @@
     <t>Hämeenlinna</t>
   </si>
   <si>
-    <t>Rytkönen/Delgado Florez</t>
-  </si>
-  <si>
-    <t>Heikkilä/Wickman</t>
-  </si>
-  <si>
-    <t>Seppänen/Mäkinen</t>
-  </si>
-  <si>
     <t>13-21,15-21</t>
   </si>
   <si>
@@ -593,21 +437,6 @@
   </si>
   <si>
     <t>Ma</t>
-  </si>
-  <si>
-    <t>Katoperä/Errkonen</t>
-  </si>
-  <si>
-    <t>Antola/Sieppi</t>
-  </si>
-  <si>
-    <t>Lindell/Heimonen</t>
-  </si>
-  <si>
-    <t>Strang/Päivärinta</t>
-  </si>
-  <si>
-    <t>Tihinen/Louhimaa</t>
   </si>
   <si>
     <t>14-21,21-12</t>
@@ -629,19 +458,245 @@
 Antola</t>
   </si>
   <si>
-    <t>Katoperä/Erkkonen</t>
-  </si>
-  <si>
     <t>28-26,21-14</t>
   </si>
   <si>
     <t>12-21,17-21</t>
   </si>
   <si>
-    <t>Niskasaari/Tihinen</t>
-  </si>
-  <si>
     <t>20-22,18-21</t>
+  </si>
+  <si>
+    <t>Mattila/
+Laurila</t>
+  </si>
+  <si>
+    <t>Vesanen/
+Rainio</t>
+  </si>
+  <si>
+    <t>Esko/
+Kerman</t>
+  </si>
+  <si>
+    <t>Laukkanen/
+Sieppi</t>
+  </si>
+  <si>
+    <t>Kuusipalo/
+Isid</t>
+  </si>
+  <si>
+    <t>Virkunen/
+Schreibmaier</t>
+  </si>
+  <si>
+    <t>Kuokkanen/
+Hiitti</t>
+  </si>
+  <si>
+    <t>Välimäki/
+Roininen</t>
+  </si>
+  <si>
+    <t>Ahonen/
+Järvi-Laturi</t>
+  </si>
+  <si>
+    <t>Nevala/
+Virtanen</t>
+  </si>
+  <si>
+    <t>Salmi/
+Lietsala</t>
+  </si>
+  <si>
+    <t>Marttila/
+Välimäki</t>
+  </si>
+  <si>
+    <t>Mattila/
+Talvia</t>
+  </si>
+  <si>
+    <t>Oivanen/
+Holm</t>
+  </si>
+  <si>
+    <t>Ruusumaa/
+Kanerva</t>
+  </si>
+  <si>
+    <t>Pöyhönen/
+Peltonen</t>
+  </si>
+  <si>
+    <t>Kerman/
+Nykänen</t>
+  </si>
+  <si>
+    <t>Nieminen/
+Rapeli</t>
+  </si>
+  <si>
+    <t>Riponiemi/
+Laine</t>
+  </si>
+  <si>
+    <t>Heimala/
+Peltonen</t>
+  </si>
+  <si>
+    <t>Huhta/
+Kumpulainen</t>
+  </si>
+  <si>
+    <t>Rainio/
+Vesanen</t>
+  </si>
+  <si>
+    <t>Katoperä/
+Paloniemi</t>
+  </si>
+  <si>
+    <t>Luoto/
+Hakamäki</t>
+  </si>
+  <si>
+    <t>Oivanen/
+Nurminen</t>
+  </si>
+  <si>
+    <t>Temisevä/
+Ylitalo</t>
+  </si>
+  <si>
+    <t>Rainio/
+Välimäki</t>
+  </si>
+  <si>
+    <t>Jokinen/
+Mäenpää</t>
+  </si>
+  <si>
+    <t>Peltonen/
+Parkkisenniemi</t>
+  </si>
+  <si>
+    <t>Uusitalo/
+Peippo</t>
+  </si>
+  <si>
+    <t>Hakala/
+Peippo</t>
+  </si>
+  <si>
+    <t>Rajala/
+Tuunainen</t>
+  </si>
+  <si>
+    <t>Heimala/
+Lehiö</t>
+  </si>
+  <si>
+    <t>Välimäki/
+Vuorentausta</t>
+  </si>
+  <si>
+    <t>Antikainen/
+Puttonen</t>
+  </si>
+  <si>
+    <t>Sieppi/
+Syri</t>
+  </si>
+  <si>
+    <t>Nurmi/
+Keränen</t>
+  </si>
+  <si>
+    <t>Kerman/
+Peltonen</t>
+  </si>
+  <si>
+    <t>Rapeli/
+Vilenius</t>
+  </si>
+  <si>
+    <t>Heimala/
+Kerman</t>
+  </si>
+  <si>
+    <t>Hakamäki/
+Luoto</t>
+  </si>
+  <si>
+    <t>Peippo/
+Uusitalo</t>
+  </si>
+  <si>
+    <t>Piispanen/
+Vilokkinen</t>
+  </si>
+  <si>
+    <t>Ruuska/
+Nauha</t>
+  </si>
+  <si>
+    <t>Heikkilä/
+Kaustinen</t>
+  </si>
+  <si>
+    <t>Katoperä/
+Setälä</t>
+  </si>
+  <si>
+    <t>Katoperä/
+Erkkonen</t>
+  </si>
+  <si>
+    <t>Sieppi/
+Antola</t>
+  </si>
+  <si>
+    <t>Vilokkinen/
+Lassila</t>
+  </si>
+  <si>
+    <t>Välimäki/
+Tuunainen</t>
+  </si>
+  <si>
+    <t>Antola/
+Sieppi</t>
+  </si>
+  <si>
+    <t>Lindell/
+Heimonen</t>
+  </si>
+  <si>
+    <t>Strang/
+Päivärinta</t>
+  </si>
+  <si>
+    <t>Tihinen/
+Louhimaa</t>
+  </si>
+  <si>
+    <t>Niskasaari/
+Tihinen</t>
+  </si>
+  <si>
+    <t>Rytkönen/
+Delgado Florez</t>
+  </si>
+  <si>
+    <t>Heikkilä/
+Wickman</t>
+  </si>
+  <si>
+    <t>Seppänen/
+Mäkinen</t>
   </si>
 </sst>
 </file>
@@ -1160,31 +1215,31 @@
         <v>4</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1"/>
     </row>
@@ -1230,7 +1285,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B3" s="10">
         <v>2023</v>
@@ -1270,7 +1325,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B4" s="12">
         <v>2024</v>
@@ -1310,7 +1365,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B5" s="10">
         <v>2025</v>
@@ -1350,7 +1405,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B6" s="12">
         <v>2025</v>
@@ -1390,7 +1445,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B7" s="10">
         <v>2026</v>
@@ -1430,7 +1485,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="B8" s="12">
         <v>2026</v>
@@ -1469,7 +1524,7 @@
     </row>
     <row r="9" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="33" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="B9" s="33"/>
       <c r="C9" s="33">
@@ -1516,7 +1571,10 @@
   <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="19" width="10.77734375" customWidth="1"/>
+    <col min="1" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1559,43 +1617,43 @@
         <v>7</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
-        <v>191</v>
+        <v>134</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="B2" s="16">
         <v>46200</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -1611,7 +1669,7 @@
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="18" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="Q2" s="12">
         <f>SUM(I2:I4)</f>
@@ -1628,28 +1686,28 @@
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="B3" s="32">
         <v>46200</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -1682,28 +1740,28 @@
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="B4" s="16">
         <v>46200</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>176</v>
+        <v>134</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>195</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -1717,9 +1775,11 @@
       <c r="N4" s="19">
         <v>42</v>
       </c>
-      <c r="O4" s="19"/>
+      <c r="O4" s="19">
+        <v>5</v>
+      </c>
       <c r="P4" s="18" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="Q4" s="12">
         <f>SUM(M2:M4)</f>
@@ -1857,7 +1917,10 @@
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="20" width="10.77734375" customWidth="1"/>
+    <col min="1" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="20" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
@@ -1900,46 +1963,46 @@
         <v>7</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B2" s="16">
         <v>46189</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -1955,7 +2018,7 @@
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="18" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="Q2" s="12">
         <f>SUM(I2:I20)+SUM(J2:J20)</f>
@@ -1976,28 +2039,28 @@
     </row>
     <row r="3" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B3" s="32">
         <v>46189</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D3" s="30" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -2031,28 +2094,28 @@
     </row>
     <row r="4" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B4" s="16">
         <v>46189</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>167</v>
+        <v>183</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -2070,7 +2133,7 @@
         <v>9</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="Q4" s="12">
         <f>SUM(M2:M4)</f>
@@ -2088,28 +2151,28 @@
     </row>
     <row r="5" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B5" s="32">
         <v>46202</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>186</v>
+        <v>129</v>
       </c>
       <c r="I5" s="30"/>
       <c r="J5" s="30"/>
@@ -2125,7 +2188,7 @@
       </c>
       <c r="O5" s="30"/>
       <c r="P5" s="29" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="Q5" s="30">
         <f>SUM(I5:I7)</f>
@@ -2143,28 +2206,28 @@
     </row>
     <row r="6" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B6" s="16">
         <v>46202</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" s="12">
@@ -2198,28 +2261,28 @@
     </row>
     <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B7" s="32">
         <v>46202</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="F7" s="35" t="s">
         <v>184</v>
       </c>
+      <c r="F7" s="30" t="s">
+        <v>190</v>
+      </c>
       <c r="G7" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="I7" s="35"/>
       <c r="J7" s="35"/>
@@ -2235,7 +2298,7 @@
       </c>
       <c r="O7" s="35"/>
       <c r="P7" s="29" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="Q7" s="30">
         <f>SUM(M5:M7)</f>
@@ -2253,28 +2316,28 @@
     </row>
     <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B8" s="16">
         <v>46202</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="12">
@@ -2308,28 +2371,28 @@
     </row>
     <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B9" s="32">
         <v>46202</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>124</v>
+        <v>184</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>168</v>
       </c>
       <c r="G9" s="36" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="I9" s="35">
         <v>1</v>
@@ -2345,7 +2408,7 @@
       </c>
       <c r="O9" s="35"/>
       <c r="P9" s="29" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="Q9" s="30">
         <f>SUM(M7:M9)</f>
@@ -2363,28 +2426,28 @@
     </row>
     <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B10" s="16">
         <v>46202</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
@@ -2407,28 +2470,28 @@
     </row>
     <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B11" s="32">
         <v>46202</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E11" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="F11" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="F11" s="35" t="s">
-        <v>195</v>
-      </c>
       <c r="G11" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="I11" s="35"/>
       <c r="J11" s="35"/>
@@ -2541,7 +2604,10 @@
   <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="19" width="10.77734375" customWidth="1"/>
+    <col min="1" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="7" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -2584,43 +2650,43 @@
         <v>7</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B2" s="16">
         <v>45851</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -2636,7 +2702,7 @@
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="18" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="Q2" s="12">
         <f>SUM(I2:I4)</f>
@@ -2653,28 +2719,28 @@
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B3" s="13">
         <v>45851</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -2707,28 +2773,28 @@
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B4" s="20">
         <v>45851</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>151</v>
+        <v>107</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>182</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -2746,7 +2812,7 @@
         <v>9</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="Q4" s="12">
         <f>SUM(M2:M4)</f>
@@ -2858,7 +2924,10 @@
   <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="19" width="10.77734375" customWidth="1"/>
+    <col min="1" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" customWidth="1"/>
+    <col min="7" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -2898,44 +2967,44 @@
         <v>7</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="O1" s="15"/>
       <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B2" s="16">
         <v>45822</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="I2" s="12">
         <v>1</v>
@@ -2951,7 +3020,7 @@
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="18" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="Q2" s="12">
         <f>SUM(I2:I28)</f>
@@ -2968,28 +3037,28 @@
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B3" s="13">
         <v>45822</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -3022,28 +3091,28 @@
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B4" s="16">
         <v>45822</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -3061,7 +3130,7 @@
       </c>
       <c r="O4" s="12"/>
       <c r="P4" s="31" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="Q4" s="12">
         <f>SUM(L2:L28)</f>
@@ -3078,28 +3147,28 @@
     </row>
     <row r="5" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B5" s="13">
         <v>45827</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I5" s="10">
         <v>1</v>
@@ -3121,28 +3190,28 @@
     </row>
     <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B6" s="16">
         <v>45827</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
@@ -3164,28 +3233,28 @@
     </row>
     <row r="7" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B7" s="13">
         <v>45827</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="I7" s="10">
         <v>1</v>
@@ -3207,28 +3276,28 @@
     </row>
     <row r="8" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B8" s="16">
         <v>45827</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
@@ -3250,28 +3319,28 @@
     </row>
     <row r="9" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B9" s="13">
         <v>45837</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
@@ -3295,28 +3364,28 @@
     </row>
     <row r="10" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B10" s="16">
         <v>45837</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>124</v>
+        <v>168</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="I10" s="12">
         <v>1</v>
@@ -3338,28 +3407,28 @@
     </row>
     <row r="11" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B11" s="13">
         <v>45837</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="I11" s="10">
         <v>1</v>
@@ -3381,28 +3450,28 @@
     </row>
     <row r="12" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B12" s="16">
         <v>45837</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
@@ -3426,28 +3495,28 @@
     </row>
     <row r="13" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B13" s="23">
         <v>45839</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>124</v>
+        <v>168</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="I13" s="10">
         <v>1</v>
@@ -3467,30 +3536,30 @@
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
     </row>
-    <row r="14" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B14" s="25">
         <v>45839</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
@@ -3512,28 +3581,28 @@
     </row>
     <row r="15" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B15" s="23">
         <v>45839</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="I15" s="10">
         <v>1</v>
@@ -3555,28 +3624,28 @@
     </row>
     <row r="16" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B16" s="25">
         <v>45839</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
@@ -3600,28 +3669,28 @@
     </row>
     <row r="17" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B17" s="23">
         <v>45844</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="I17" s="10">
         <v>1</v>
@@ -3643,28 +3712,28 @@
     </row>
     <row r="18" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B18" s="25">
         <v>45844</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
@@ -3686,28 +3755,28 @@
     </row>
     <row r="19" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B19" s="23">
         <v>45844</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="I19" s="10">
         <v>1</v>
@@ -3729,28 +3798,28 @@
     </row>
     <row r="20" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B20" s="25">
         <v>45844</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
@@ -3772,9 +3841,9 @@
       <c r="R20" s="12"/>
       <c r="S20" s="12"/>
     </row>
-    <row r="21" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B21" s="23">
         <v>45868</v>
@@ -3783,19 +3852,19 @@
         <v>9</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
@@ -3817,7 +3886,7 @@
     </row>
     <row r="22" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B22" s="25">
         <v>45868</v>
@@ -3826,19 +3895,19 @@
         <v>9</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
@@ -3860,7 +3929,7 @@
     </row>
     <row r="23" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B23" s="23">
         <v>45868</v>
@@ -3869,19 +3938,19 @@
         <v>9</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
@@ -3903,7 +3972,7 @@
     </row>
     <row r="24" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B24" s="25">
         <v>45868</v>
@@ -3912,19 +3981,19 @@
         <v>9</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="I24" s="12">
         <v>1</v>
@@ -3948,28 +4017,28 @@
     </row>
     <row r="25" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B25" s="23">
         <v>46608</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I25" s="10">
         <v>1</v>
@@ -3991,28 +4060,28 @@
     </row>
     <row r="26" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B26" s="25">
         <v>46608</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
@@ -4034,28 +4103,28 @@
     </row>
     <row r="27" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B27" s="23">
         <v>46608</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="I27" s="10">
         <v>1</v>
@@ -4077,28 +4146,28 @@
     </row>
     <row r="28" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B28" s="25">
         <v>46608</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
@@ -4194,7 +4263,10 @@
   <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="19" width="10.77734375" customWidth="1"/>
+    <col min="1" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="7" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -4234,44 +4306,44 @@
         <v>7</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="O1" s="15"/>
       <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B2" s="16">
         <v>45423</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -4287,7 +4359,7 @@
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="18" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="Q2" s="12">
         <f>SUM(I2:I13)</f>
@@ -4304,28 +4376,28 @@
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B3" s="13">
         <v>45423</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -4358,28 +4430,28 @@
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B4" s="16">
         <v>45423</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -4397,7 +4469,7 @@
       </c>
       <c r="O4" s="12"/>
       <c r="P4" s="18" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="Q4" s="12">
         <f>SUM(L3:L13)</f>
@@ -4414,28 +4486,28 @@
     </row>
     <row r="5" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B5" s="13">
         <v>45458</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>90</v>
+        <v>153</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
@@ -4457,28 +4529,28 @@
     </row>
     <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B6" s="16">
         <v>45458</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>92</v>
+        <v>154</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
@@ -4500,28 +4572,28 @@
     </row>
     <row r="7" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B7" s="13">
         <v>45458</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
@@ -4543,28 +4615,28 @@
     </row>
     <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B8" s="16">
         <v>45458</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
@@ -4588,28 +4660,28 @@
     </row>
     <row r="9" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B9" s="23">
         <v>45461</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
@@ -4631,28 +4703,28 @@
     </row>
     <row r="10" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B10" s="25">
         <v>45461</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
@@ -4674,28 +4746,28 @@
     </row>
     <row r="11" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B11" s="23">
         <v>45461</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>92</v>
+        <v>154</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
@@ -4715,30 +4787,30 @@
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
     </row>
-    <row r="12" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B12" s="25">
         <v>45461</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="I12" s="12">
         <v>1</v>
@@ -4760,28 +4832,28 @@
     </row>
     <row r="13" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B13" s="23">
         <v>45461</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>104</v>
+        <v>159</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
@@ -4818,7 +4890,10 @@
   <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="19" width="10.77734375" customWidth="1"/>
+    <col min="1" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="7" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -4858,46 +4933,46 @@
         <v>7</v>
       </c>
       <c r="N1" s="27" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="O1" s="15"/>
       <c r="P1" s="11" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B2" s="16">
         <v>45107</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -4912,7 +4987,7 @@
       </c>
       <c r="N2" s="12"/>
       <c r="O2" s="18" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="P2" s="12">
         <f>SUM(I2:I13)</f>
@@ -4933,28 +5008,28 @@
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B3" s="13">
         <v>45107</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>44</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -4987,28 +5062,28 @@
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B4" s="16">
         <v>45107</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>45</v>
-      </c>
       <c r="G4" s="17" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12">
@@ -5023,7 +5098,7 @@
       </c>
       <c r="N4" s="12"/>
       <c r="O4" s="18" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="P4" s="12">
         <f>SUM(L2:L13)</f>
@@ -5041,28 +5116,28 @@
     </row>
     <row r="5" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B5" s="13">
         <v>45107</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10">
@@ -5084,28 +5159,28 @@
     </row>
     <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B6" s="16">
         <v>45107</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
@@ -5129,7 +5204,7 @@
     </row>
     <row r="7" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B7" s="13">
         <v>45112</v>
@@ -5138,19 +5213,19 @@
         <v>9</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
@@ -5172,7 +5247,7 @@
     </row>
     <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B8" s="16">
         <v>45112</v>
@@ -5181,19 +5256,19 @@
         <v>9</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
@@ -5215,7 +5290,7 @@
     </row>
     <row r="9" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B9" s="13">
         <v>45112</v>
@@ -5224,19 +5299,19 @@
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I9" s="10">
         <v>1</v>
@@ -5258,7 +5333,7 @@
     </row>
     <row r="10" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B10" s="16">
         <v>45112</v>
@@ -5267,19 +5342,19 @@
         <v>9</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
@@ -5303,28 +5378,28 @@
     </row>
     <row r="11" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B11" s="13">
         <v>45122</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
@@ -5346,28 +5421,28 @@
     </row>
     <row r="12" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B12" s="16">
         <v>45122</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
@@ -5389,28 +5464,28 @@
     </row>
     <row r="13" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B13" s="13">
         <v>45122</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
@@ -5443,7 +5518,10 @@
   <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="18" width="10.77734375" customWidth="1"/>
+    <col min="1" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" customWidth="1"/>
+    <col min="7" max="18" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
@@ -5483,17 +5561,17 @@
         <v>7</v>
       </c>
       <c r="N1" s="27" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="O1" s="11"/>
       <c r="P1" s="11" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
@@ -5534,7 +5612,7 @@
       </c>
       <c r="N2" s="12"/>
       <c r="O2" s="18" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="P2" s="12">
         <f>SUM(I2:I13)</f>
@@ -5566,13 +5644,13 @@
         <v>11</v>
       </c>
       <c r="F3" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="H3" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>17</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -5619,13 +5697,13 @@
         <v>11</v>
       </c>
       <c r="F4" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="12" t="s">
         <v>18</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>20</v>
       </c>
       <c r="I4" s="12">
         <v>1</v>
@@ -5640,7 +5718,7 @@
       </c>
       <c r="N4" s="12"/>
       <c r="O4" s="18" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="P4" s="12">
         <f>SUM(L2:L13)</f>
@@ -5672,13 +5750,13 @@
         <v>11</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="G5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="28" t="s">
         <v>19</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>22</v>
       </c>
       <c r="I5" s="10">
         <v>1</v>
@@ -5714,13 +5792,13 @@
         <v>11</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>13</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I6" s="12">
         <v>1</v>
@@ -5756,13 +5834,13 @@
         <v>11</v>
       </c>
       <c r="F7" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>16</v>
-      </c>
       <c r="H7" s="10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
@@ -5791,22 +5869,22 @@
         <v>45095</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>28</v>
+        <v>141</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I8" s="12">
         <v>1</v>
@@ -5833,22 +5911,22 @@
         <v>45095</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I9" s="10">
         <v>1</v>
@@ -5875,10 +5953,10 @@
         <v>45095</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>11</v>
@@ -5887,10 +5965,10 @@
         <v>12</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I10" s="12">
         <v>1</v>
@@ -5909,7 +5987,7 @@
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
     </row>
-    <row r="11" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
@@ -5917,22 +5995,22 @@
         <v>45095</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I11" s="10">
         <v>1</v>
@@ -5959,22 +6037,22 @@
         <v>45095</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I12" s="12">
         <v>1</v>
@@ -6001,22 +6079,22 @@
         <v>45095</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9DFDA4-81C5-4A3E-9736-E7A88FDB7E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6050010A-97B8-4CE4-94C0-23A1A33125F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="195">
   <si>
     <t>sarja</t>
   </si>
@@ -149,9 +149,6 @@
     <t>Jyväskylä</t>
   </si>
   <si>
-    <t>Viljamaa/Kuikka</t>
-  </si>
-  <si>
     <t>8-21,12-21</t>
   </si>
   <si>
@@ -159,37 +156,22 @@
 Huttunen</t>
   </si>
   <si>
-    <t>Poikonen/Saloranta</t>
-  </si>
-  <si>
     <t>16-21,8-21</t>
   </si>
   <si>
-    <t>Nevala/Hietanen</t>
-  </si>
-  <si>
     <t>1-1</t>
   </si>
   <si>
     <t>21-14,19-21</t>
   </si>
   <si>
-    <t>Ruusumaa/Kanerva</t>
-  </si>
-  <si>
     <t>14-21,21-17</t>
   </si>
   <si>
-    <t>Harmanen/Kuronen</t>
-  </si>
-  <si>
     <t>18-21,21-18,4-15</t>
   </si>
   <si>
     <t>Helsinki</t>
-  </si>
-  <si>
-    <t>Roininen/Peräsalo</t>
   </si>
   <si>
     <t>12-21,9-21</t>
@@ -697,6 +679,26 @@
   <si>
     <t>Seppänen/
 Mäkinen</t>
+  </si>
+  <si>
+    <t>Viljamaa/
+Kuikka</t>
+  </si>
+  <si>
+    <t>Poikonen/
+Saloranta</t>
+  </si>
+  <si>
+    <t>Nevala/
+Hietanen</t>
+  </si>
+  <si>
+    <t>Harmanen/
+Kuronen</t>
+  </si>
+  <si>
+    <t>Roininen/
+Peräsalo</t>
   </si>
 </sst>
 </file>
@@ -1215,31 +1217,31 @@
         <v>4</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>68</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>74</v>
       </c>
       <c r="K1" s="1"/>
     </row>
@@ -1405,7 +1407,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B6" s="12">
         <v>2025</v>
@@ -1445,7 +1447,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B7" s="10">
         <v>2026</v>
@@ -1485,7 +1487,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B8" s="12">
         <v>2026</v>
@@ -1524,7 +1526,7 @@
     </row>
     <row r="9" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="33" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B9" s="33"/>
       <c r="C9" s="33">
@@ -1571,9 +1573,8 @@
   <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="10.77734375" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="1" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="6" width="14.77734375" customWidth="1"/>
     <col min="7" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1617,43 +1618,43 @@
         <v>7</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B2" s="16">
         <v>46200</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G2" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -1669,7 +1670,7 @@
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="18" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q2" s="12">
         <f>SUM(I2:I4)</f>
@@ -1686,28 +1687,28 @@
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B3" s="32">
         <v>46200</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -1740,28 +1741,28 @@
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B4" s="16">
         <v>46200</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="G4" s="21" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -1779,7 +1780,7 @@
         <v>5</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Q4" s="12">
         <f>SUM(M2:M4)</f>
@@ -1917,9 +1918,8 @@
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="10.77734375" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="1" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="6" width="14.77734375" customWidth="1"/>
     <col min="7" max="20" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1963,46 +1963,46 @@
         <v>7</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B2" s="16">
         <v>46189</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G2" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="18" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q2" s="12">
         <f>SUM(I2:I20)+SUM(J2:J20)</f>
@@ -2039,28 +2039,28 @@
     </row>
     <row r="3" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B3" s="32">
         <v>46189</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D3" s="30" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -2094,28 +2094,28 @@
     </row>
     <row r="4" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B4" s="16">
         <v>46189</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G4" s="21" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -2133,7 +2133,7 @@
         <v>9</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Q4" s="12">
         <f>SUM(M2:M4)</f>
@@ -2151,28 +2151,28 @@
     </row>
     <row r="5" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B5" s="32">
         <v>46202</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="I5" s="30"/>
       <c r="J5" s="30"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O5" s="30"/>
       <c r="P5" s="29" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q5" s="30">
         <f>SUM(I5:I7)</f>
@@ -2206,28 +2206,28 @@
     </row>
     <row r="6" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B6" s="16">
         <v>46202</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" s="12">
@@ -2261,28 +2261,28 @@
     </row>
     <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B7" s="32">
         <v>46202</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D7" s="30" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="F7" s="30" t="s">
         <v>184</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>190</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I7" s="35"/>
       <c r="J7" s="35"/>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="O7" s="35"/>
       <c r="P7" s="29" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Q7" s="30">
         <f>SUM(M5:M7)</f>
@@ -2316,28 +2316,28 @@
     </row>
     <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16">
         <v>46202</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G8" s="17" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="12">
@@ -2371,28 +2371,28 @@
     </row>
     <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B9" s="32">
         <v>46202</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G9" s="36" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="I9" s="35">
         <v>1</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="O9" s="35"/>
       <c r="P9" s="29" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Q9" s="30">
         <f>SUM(M7:M9)</f>
@@ -2426,28 +2426,28 @@
     </row>
     <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B10" s="16">
         <v>46202</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
@@ -2470,28 +2470,28 @@
     </row>
     <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B11" s="32">
         <v>46202</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D11" s="30" t="s">
         <v>33</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I11" s="35"/>
       <c r="J11" s="35"/>
@@ -2604,9 +2604,8 @@
   <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="10.77734375" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="1" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="6" width="14.77734375" customWidth="1"/>
     <col min="7" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2650,22 +2649,22 @@
         <v>7</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B2" s="16">
         <v>45851</v>
@@ -2674,19 +2673,19 @@
         <v>22</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G2" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -2702,7 +2701,7 @@
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="18" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q2" s="12">
         <f>SUM(I2:I4)</f>
@@ -2719,7 +2718,7 @@
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B3" s="13">
         <v>45851</v>
@@ -2728,19 +2727,19 @@
         <v>22</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -2773,7 +2772,7 @@
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B4" s="20">
         <v>45851</v>
@@ -2782,19 +2781,19 @@
         <v>22</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G4" s="21" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -2812,7 +2811,7 @@
         <v>9</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Q4" s="12">
         <f>SUM(M2:M4)</f>
@@ -2924,9 +2923,8 @@
   <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="10.77734375" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" customWidth="1"/>
+    <col min="1" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="6" width="14.77734375" customWidth="1"/>
     <col min="7" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2967,18 +2965,18 @@
         <v>7</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="O1" s="15"/>
       <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -2989,22 +2987,22 @@
         <v>45822</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>23</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G2" s="17" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I2" s="12">
         <v>1</v>
@@ -3020,7 +3018,7 @@
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="18" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q2" s="12">
         <f>SUM(I2:I28)</f>
@@ -3043,22 +3041,22 @@
         <v>45822</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>29</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -3097,22 +3095,22 @@
         <v>45822</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -3130,7 +3128,7 @@
       </c>
       <c r="O4" s="12"/>
       <c r="P4" s="31" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Q4" s="12">
         <f>SUM(L2:L28)</f>
@@ -3153,22 +3151,22 @@
         <v>45827</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I5" s="10">
         <v>1</v>
@@ -3196,22 +3194,22 @@
         <v>45827</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
@@ -3239,22 +3237,22 @@
         <v>45827</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="I7" s="10">
         <v>1</v>
@@ -3282,22 +3280,22 @@
         <v>45827</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>166</v>
       </c>
       <c r="G8" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
@@ -3325,22 +3323,22 @@
         <v>45837</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
@@ -3370,22 +3368,22 @@
         <v>45837</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I10" s="12">
         <v>1</v>
@@ -3413,22 +3411,22 @@
         <v>45837</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I11" s="10">
         <v>1</v>
@@ -3456,22 +3454,22 @@
         <v>45837</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
@@ -3501,22 +3499,22 @@
         <v>45839</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>33</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="I13" s="10">
         <v>1</v>
@@ -3544,22 +3542,22 @@
         <v>45839</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G14" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
@@ -3587,22 +3585,22 @@
         <v>45839</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>33</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G15" s="14" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="I15" s="10">
         <v>1</v>
@@ -3630,22 +3628,22 @@
         <v>45839</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G16" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
@@ -3678,19 +3676,19 @@
         <v>22</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G17" s="14" t="s">
         <v>17</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="I17" s="10">
         <v>1</v>
@@ -3721,19 +3719,19 @@
         <v>22</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G18" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
@@ -3764,19 +3762,19 @@
         <v>22</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>17</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="I19" s="10">
         <v>1</v>
@@ -3807,19 +3805,19 @@
         <v>22</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G20" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
@@ -3852,19 +3850,19 @@
         <v>9</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G21" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
@@ -3895,19 +3893,19 @@
         <v>9</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G22" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
@@ -3938,19 +3936,19 @@
         <v>9</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G23" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
@@ -3981,19 +3979,19 @@
         <v>9</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G24" s="17" t="s">
         <v>17</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I24" s="12">
         <v>1</v>
@@ -4023,16 +4021,16 @@
         <v>46608</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G25" s="14" t="s">
         <v>17</v>
@@ -4066,22 +4064,22 @@
         <v>46608</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
@@ -4109,22 +4107,22 @@
         <v>46608</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="I27" s="10">
         <v>1</v>
@@ -4152,22 +4150,22 @@
         <v>46608</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G28" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
@@ -4263,9 +4261,8 @@
   <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="10.77734375" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="1" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="6" width="14.77734375" customWidth="1"/>
     <col min="7" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4306,18 +4303,18 @@
         <v>7</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="O1" s="15"/>
       <c r="P1" s="15"/>
       <c r="Q1" s="11" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -4328,22 +4325,22 @@
         <v>45423</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G2" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -4359,7 +4356,7 @@
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="18" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q2" s="12">
         <f>SUM(I2:I13)</f>
@@ -4382,22 +4379,22 @@
         <v>45423</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -4436,22 +4433,22 @@
         <v>45423</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -4469,7 +4466,7 @@
       </c>
       <c r="O4" s="12"/>
       <c r="P4" s="18" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Q4" s="12">
         <f>SUM(L3:L13)</f>
@@ -4492,22 +4489,22 @@
         <v>45458</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
@@ -4535,16 +4532,16 @@
         <v>45458</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>15</v>
@@ -4578,22 +4575,22 @@
         <v>45458</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>23</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
@@ -4621,22 +4618,22 @@
         <v>45458</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G8" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
@@ -4666,22 +4663,22 @@
         <v>45461</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
@@ -4709,22 +4706,22 @@
         <v>45461</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
@@ -4752,22 +4749,22 @@
         <v>45461</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
@@ -4787,7 +4784,7 @@
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
     </row>
-    <row r="12" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>31</v>
       </c>
@@ -4795,22 +4792,22 @@
         <v>45461</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>17</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I12" s="12">
         <v>1</v>
@@ -4838,22 +4835,22 @@
         <v>45461</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
@@ -4890,9 +4887,8 @@
   <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="10.77734375" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="1" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="6" width="14.77734375" customWidth="1"/>
     <col min="7" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4933,20 +4929,20 @@
         <v>7</v>
       </c>
       <c r="N1" s="27" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="O1" s="15"/>
       <c r="P1" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -4963,16 +4959,16 @@
         <v>33</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>34</v>
+        <v>190</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -4987,7 +4983,7 @@
       </c>
       <c r="N2" s="12"/>
       <c r="O2" s="18" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="P2" s="12">
         <f>SUM(I2:I13)</f>
@@ -5020,16 +5016,16 @@
         <v>33</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>37</v>
+        <v>191</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -5074,16 +5070,16 @@
         <v>33</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12">
@@ -5098,7 +5094,7 @@
       </c>
       <c r="N4" s="12"/>
       <c r="O4" s="18" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="P4" s="12">
         <f>SUM(L2:L13)</f>
@@ -5128,16 +5124,16 @@
         <v>33</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10">
@@ -5171,16 +5167,16 @@
         <v>33</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>29</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
@@ -5213,19 +5209,19 @@
         <v>9</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>47</v>
+        <v>194</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
@@ -5256,19 +5252,19 @@
         <v>9</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G8" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
@@ -5299,19 +5295,19 @@
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I9" s="10">
         <v>1</v>
@@ -5342,19 +5338,19 @@
         <v>9</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
@@ -5384,22 +5380,22 @@
         <v>45122</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
@@ -5427,22 +5423,22 @@
         <v>45122</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
@@ -5470,22 +5466,22 @@
         <v>45122</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
@@ -5518,9 +5514,8 @@
   <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="10.77734375" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" customWidth="1"/>
+    <col min="1" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="6" width="14.77734375" customWidth="1"/>
     <col min="7" max="18" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5561,17 +5556,17 @@
         <v>7</v>
       </c>
       <c r="N1" s="27" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="O1" s="11"/>
       <c r="P1" s="11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
@@ -5612,7 +5607,7 @@
       </c>
       <c r="N2" s="12"/>
       <c r="O2" s="18" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="P2" s="12">
         <f>SUM(I2:I13)</f>
@@ -5644,7 +5639,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>15</v>
@@ -5697,7 +5692,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>17</v>
@@ -5718,7 +5713,7 @@
       </c>
       <c r="N4" s="12"/>
       <c r="O4" s="18" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="P4" s="12">
         <f>SUM(L2:L13)</f>
@@ -5750,7 +5745,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>17</v>
@@ -5792,7 +5787,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>13</v>
@@ -5834,7 +5829,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>15</v>
@@ -5878,7 +5873,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>17</v>
@@ -5920,7 +5915,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>17</v>
@@ -5987,7 +5982,7 @@
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
     </row>
-    <row r="11" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
@@ -6004,7 +5999,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>17</v>
@@ -6046,7 +6041,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>17</v>
@@ -6088,7 +6083,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>29</v>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6050010A-97B8-4CE4-94C0-23A1A33125F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0CD4CA-2341-49EB-8F1C-E2254734395D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="201">
   <si>
     <t>sarja</t>
   </si>
@@ -699,6 +699,26 @@
   <si>
     <t>Roininen/
 Peräsalo</t>
+  </si>
+  <si>
+    <t>Hietsu Helsinki</t>
+  </si>
+  <si>
+    <t>Kenttä/
+Karjalainen</t>
+  </si>
+  <si>
+    <t>Saarimaa/
+Heinonen</t>
+  </si>
+  <si>
+    <t>11-21,2-21</t>
+  </si>
+  <si>
+    <t>Peippo/Peippo</t>
+  </si>
+  <si>
+    <t>18-21,18-21</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1514,7 @@
       </c>
       <c r="C8" s="12">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" s="12">
         <f>JNCT_2026!Q3</f>
@@ -1505,7 +1525,7 @@
       </c>
       <c r="F8" s="12">
         <f>JNCT_2026!S2</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G8" s="12">
         <f>JNCT_2026!Q3</f>
@@ -1513,15 +1533,15 @@
       </c>
       <c r="H8" s="12">
         <f>JNCT_2026!R3</f>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I8" s="12">
         <f>JNCT_2026!Q4</f>
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="J8" s="12">
         <f>JNCT_2026!R4</f>
-        <v>126</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1531,7 +1551,7 @@
       <c r="B9" s="33"/>
       <c r="C9" s="33">
         <f>SUM(C2:C8)</f>
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D9" s="33">
         <f t="shared" ref="D9:J9" si="1">SUM(D2:D8)</f>
@@ -1543,7 +1563,7 @@
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G9" s="33">
         <f t="shared" si="1"/>
@@ -1551,15 +1571,15 @@
       </c>
       <c r="H9" s="33">
         <f t="shared" si="1"/>
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I9" s="33">
         <f t="shared" si="1"/>
-        <v>2346</v>
+        <v>2419</v>
       </c>
       <c r="J9" s="33">
         <f t="shared" si="1"/>
-        <v>2625</v>
+        <v>2751</v>
       </c>
     </row>
   </sheetData>
@@ -1673,16 +1693,16 @@
         <v>113</v>
       </c>
       <c r="Q2" s="12">
-        <f>SUM(I2:I4)</f>
+        <f>SUM(I2:I12)</f>
         <v>0</v>
       </c>
       <c r="R2" s="12">
-        <f>SUM(L2:L4)</f>
-        <v>3</v>
+        <f>SUM(L2:L12)</f>
+        <v>6</v>
       </c>
       <c r="S2" s="12">
         <f>SUM(Q2:R2)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1727,16 +1747,16 @@
         <v>7</v>
       </c>
       <c r="Q3" s="30">
-        <f>SUM(I3:I21)*3+SUM(J3:J21)</f>
+        <f>SUM(I2:I12)*3+SUM(J2:J12)</f>
         <v>0</v>
       </c>
       <c r="R3" s="30">
-        <f>SUM(K2:K4)*1+SUM(L2:L4)*3</f>
-        <v>9</v>
+        <f>SUM(K2:K12)*1+SUM(L2:L12)*3</f>
+        <v>18</v>
       </c>
       <c r="S3" s="30">
         <f>SUM(Q3:R3)</f>
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1783,78 +1803,330 @@
         <v>58</v>
       </c>
       <c r="Q4" s="12">
-        <f>SUM(M2:M4)</f>
-        <v>79</v>
+        <f>SUM(M2:M12)</f>
+        <v>152</v>
       </c>
       <c r="R4" s="12">
-        <f>SUM(N2:N4)</f>
-        <v>126</v>
+        <f>SUM(N2:N12)</f>
+        <v>252</v>
       </c>
       <c r="S4" s="12">
         <f>SUM(Q4:R4)</f>
-        <v>205</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B5" s="2"/>
-      <c r="E5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B6" s="2"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B7" s="2"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="7"/>
+        <v>404</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="32">
+        <v>46205</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10">
+        <v>1</v>
+      </c>
+      <c r="M5" s="10">
+        <v>24</v>
+      </c>
+      <c r="N5" s="10">
+        <v>42</v>
+      </c>
+      <c r="O5" s="10"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+    </row>
+    <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="16">
+        <v>46205</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19">
+        <v>1</v>
+      </c>
+      <c r="M6" s="19">
+        <v>13</v>
+      </c>
+      <c r="N6" s="19">
+        <v>42</v>
+      </c>
+      <c r="O6" s="19"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+    </row>
+    <row r="7" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="32">
+        <v>46205</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10">
+        <v>1</v>
+      </c>
+      <c r="M7" s="10">
+        <v>36</v>
+      </c>
+      <c r="N7" s="10">
+        <v>42</v>
+      </c>
+      <c r="O7" s="10"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B8" s="2"/>
-      <c r="E8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="8"/>
+      <c r="A8" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B9" s="2"/>
-      <c r="E9" s="3"/>
-      <c r="G9" s="4"/>
+      <c r="A9" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="32"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="2"/>
-      <c r="E10" s="3"/>
-      <c r="G10" s="4"/>
+      <c r="A10" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="2"/>
-      <c r="E11" s="3"/>
-      <c r="G11" s="4"/>
+      <c r="A11" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B12" s="2"/>
-      <c r="E12" s="3"/>
-      <c r="G12" s="4"/>
+      <c r="A12" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B13" s="9"/>
-      <c r="E13" s="3"/>
-      <c r="G13" s="4"/>
+      <c r="A13" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="9"/>
-      <c r="E14" s="3"/>
-      <c r="G14" s="4"/>
+      <c r="A14" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="9"/>
-      <c r="E15" s="3"/>
-      <c r="G15" s="4"/>
+      <c r="A15" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="32"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="30"/>
+      <c r="S15" s="30"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B16" s="9"/>
@@ -1896,15 +2168,15 @@
       </c>
       <c r="L23">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <f t="shared" si="0"/>
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="N23">
         <f t="shared" si="0"/>
-        <v>126</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -3272,7 +3544,7 @@
       <c r="R7" s="10"/>
       <c r="S7" s="10"/>
     </row>
-    <row r="8" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>31</v>
       </c>
@@ -3534,7 +3806,7 @@
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
     </row>
-    <row r="14" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>31</v>
       </c>
@@ -3839,7 +4111,7 @@
       <c r="R20" s="12"/>
       <c r="S20" s="12"/>
     </row>
-    <row r="21" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>31</v>
       </c>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0CD4CA-2341-49EB-8F1C-E2254734395D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B85F82C-FFBE-4D74-9FD5-715099FBECC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1848" yWindow="1848" windowWidth="19992" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="4" r:id="rId1"/>
@@ -1938,7 +1938,9 @@
       <c r="N7" s="10">
         <v>42</v>
       </c>
-      <c r="O7" s="10"/>
+      <c r="O7" s="10">
+        <v>17</v>
+      </c>
       <c r="P7" s="29"/>
       <c r="Q7" s="30"/>
       <c r="R7" s="30"/>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B85F82C-FFBE-4D74-9FD5-715099FBECC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA6EC56-ACED-4F78-BC30-0D7E482F5A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1848" yWindow="1848" windowWidth="19992" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1848" yWindow="0" windowWidth="19992" windowHeight="13776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="203">
   <si>
     <t>sarja</t>
   </si>
@@ -719,6 +719,14 @@
   </si>
   <si>
     <t>18-21,18-21</t>
+  </si>
+  <si>
+    <t>Pöyhönen/
+Mansikkala</t>
+  </si>
+  <si>
+    <t>Uusitalo/
+Wentus</t>
   </si>
 </sst>
 </file>
@@ -2788,13 +2796,25 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+    <row r="12" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="16">
+        <v>46207</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>201</v>
+      </c>
       <c r="G12" s="17"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
@@ -2810,13 +2830,23 @@
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="35"/>
+      <c r="B13" s="32">
+        <v>46207</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>202</v>
+      </c>
       <c r="G13" s="36"/>
       <c r="H13" s="35"/>
       <c r="I13" s="35"/>
@@ -2832,15 +2862,65 @@
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B14" s="9"/>
-      <c r="E14" s="3"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B15" s="9"/>
-      <c r="E15" s="3"/>
-      <c r="G15" s="4"/>
+    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16">
+        <v>46207</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+    </row>
+    <row r="15" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="32"/>
+      <c r="B15" s="32">
+        <v>46207</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="F15" s="35"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="30"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="30"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B16" s="9"/>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA6EC56-ACED-4F78-BC30-0D7E482F5A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713717D3-8632-4678-B700-8E457B03D48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1848" yWindow="0" windowWidth="19992" windowHeight="13776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1764" yWindow="1848" windowWidth="21276" windowHeight="11292" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="210">
   <si>
     <t>sarja</t>
   </si>
@@ -727,6 +727,29 @@
   <si>
     <t>Uusitalo/
 Wentus</t>
+  </si>
+  <si>
+    <t>21-11,21-19</t>
+  </si>
+  <si>
+    <t>9-21,12-21</t>
+  </si>
+  <si>
+    <t>Kreivilä/
+Valtanen</t>
+  </si>
+  <si>
+    <t>21-10,18-21,15-5</t>
+  </si>
+  <si>
+    <t>Nurminen/
+Peippo</t>
+  </si>
+  <si>
+    <t>20-22,21-18,15-9</t>
+  </si>
+  <si>
+    <t>12-21,12-21</t>
   </si>
 </sst>
 </file>
@@ -855,7 +878,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -952,6 +975,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1482,11 +1508,11 @@
       </c>
       <c r="C7" s="10">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D7" s="10">
         <f>U18_2026!Q2</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" s="10">
         <f>U18_2026!R2</f>
@@ -1494,15 +1520,15 @@
       </c>
       <c r="F7" s="10">
         <f>U18_2026!T2</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G7" s="10">
         <f>U18_2026!Q3</f>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H7" s="10">
         <f>U18_2026!S3</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I7" s="10">
         <f>U18_2026!Q4</f>
@@ -1559,11 +1585,11 @@
       <c r="B9" s="33"/>
       <c r="C9" s="33">
         <f>SUM(C2:C8)</f>
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D9" s="33">
         <f t="shared" ref="D9:J9" si="1">SUM(D2:D8)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E9" s="33">
         <f t="shared" si="1"/>
@@ -1571,15 +1597,15 @@
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G9" s="33">
         <f t="shared" si="1"/>
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H9" s="33">
         <f t="shared" si="1"/>
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="I9" s="33">
         <f t="shared" si="1"/>
@@ -2202,7 +2228,9 @@
   <cols>
     <col min="1" max="3" width="10.77734375" customWidth="1"/>
     <col min="4" max="6" width="14.77734375" customWidth="1"/>
-    <col min="7" max="20" width="10.77734375" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="9" max="20" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
@@ -2304,7 +2332,7 @@
       </c>
       <c r="Q2" s="12">
         <f>SUM(I2:I20)+SUM(J2:J20)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R2" s="12">
         <f>SUM(K2:K20)</f>
@@ -2312,11 +2340,11 @@
       </c>
       <c r="S2" s="12">
         <f>SUM(L2:L20)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T2" s="12">
         <f t="shared" ref="T2:T9" si="0">SUM(Q2:S2)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -2362,16 +2390,16 @@
       </c>
       <c r="Q3" s="30">
         <f>SUM(I2:I20)*3+SUM(J2:J20)*2+SUM(K2:K20)</f>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R3" s="30"/>
       <c r="S3" s="30">
         <f>SUM(K2:K20)*1+SUM(L2:L20)*3</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="T3" s="30">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -2529,7 +2557,7 @@
       </c>
       <c r="Q6" s="12">
         <f>SUM(I6:I24)*3+SUM(J6:J24)</f>
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R6" s="12"/>
       <c r="S6" s="12">
@@ -2538,7 +2566,7 @@
       </c>
       <c r="T6" s="12">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -2639,7 +2667,7 @@
       </c>
       <c r="Q8" s="12">
         <f>SUM(I8:I26)*3+SUM(J8:J26)</f>
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R8" s="12"/>
       <c r="S8" s="12">
@@ -2648,7 +2676,7 @@
       </c>
       <c r="T8" s="12">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -2815,14 +2843,24 @@
       <c r="F12" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="G12" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="I12" s="12">
+        <v>1</v>
+      </c>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
       <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
+      <c r="M12" s="12">
+        <v>42</v>
+      </c>
+      <c r="N12" s="12">
+        <v>30</v>
+      </c>
       <c r="O12" s="12"/>
       <c r="P12" s="18"/>
       <c r="Q12" s="12"/>
@@ -2831,7 +2869,9 @@
       <c r="T12" s="12"/>
     </row>
     <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="32"/>
+      <c r="A13" s="32" t="s">
+        <v>99</v>
+      </c>
       <c r="B13" s="32">
         <v>46207</v>
       </c>
@@ -2847,14 +2887,24 @@
       <c r="F13" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="G13" s="36"/>
-      <c r="H13" s="35"/>
+      <c r="G13" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="35" t="s">
+        <v>204</v>
+      </c>
       <c r="I13" s="35"/>
       <c r="J13" s="35"/>
       <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
+      <c r="L13" s="35">
+        <v>1</v>
+      </c>
+      <c r="M13" s="35">
+        <v>21</v>
+      </c>
+      <c r="N13" s="35">
+        <v>42</v>
+      </c>
       <c r="O13" s="35"/>
       <c r="P13" s="29"/>
       <c r="Q13" s="30"/>
@@ -2863,7 +2913,9 @@
       <c r="T13" s="30"/>
     </row>
     <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
+      <c r="A14" s="16" t="s">
+        <v>99</v>
+      </c>
       <c r="B14" s="16">
         <v>46207</v>
       </c>
@@ -2876,15 +2928,27 @@
       <c r="E14" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
+      <c r="F14" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="I14" s="12">
+        <v>1</v>
+      </c>
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
       <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
+      <c r="M14" s="12">
+        <v>54</v>
+      </c>
+      <c r="N14" s="12">
+        <v>36</v>
+      </c>
       <c r="O14" s="12"/>
       <c r="P14" s="18"/>
       <c r="Q14" s="12"/>
@@ -2893,7 +2957,9 @@
       <c r="T14" s="12"/>
     </row>
     <row r="15" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="32"/>
+      <c r="A15" s="32" t="s">
+        <v>99</v>
+      </c>
       <c r="B15" s="32">
         <v>46207</v>
       </c>
@@ -2906,15 +2972,27 @@
       <c r="E15" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="F15" s="35"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
+      <c r="F15" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="I15" s="35">
+        <v>1</v>
+      </c>
       <c r="J15" s="35"/>
       <c r="K15" s="35"/>
       <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
+      <c r="M15" s="35">
+        <v>56</v>
+      </c>
+      <c r="N15" s="35">
+        <v>49</v>
+      </c>
       <c r="O15" s="35"/>
       <c r="P15" s="29"/>
       <c r="Q15" s="30"/>
@@ -2922,10 +3000,49 @@
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B16" s="9"/>
-      <c r="E16" s="3"/>
-      <c r="G16" s="4"/>
+    <row r="16" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="16">
+        <v>46207</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12">
+        <v>1</v>
+      </c>
+      <c r="M16" s="12">
+        <v>24</v>
+      </c>
+      <c r="N16" s="12">
+        <v>42</v>
+      </c>
+      <c r="O16" s="12"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="9"/>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713717D3-8632-4678-B700-8E457B03D48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64809470-729F-4D82-BD22-3175A6131717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1764" yWindow="1848" windowWidth="21276" windowHeight="11292" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="21276" windowHeight="12948" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="213">
   <si>
     <t>sarja</t>
   </si>
@@ -750,6 +750,18 @@
   </si>
   <si>
     <t>12-21,12-21</t>
+  </si>
+  <si>
+    <t>Mäntylä/
+Katoperä</t>
+  </si>
+  <si>
+    <t>Ruusumaa/
+Niemi</t>
+  </si>
+  <si>
+    <t>Paajanen/
+Puolakka</t>
   </si>
 </sst>
 </file>
@@ -1980,15 +1992,25 @@
       <c r="R7" s="30"/>
       <c r="S7" s="30"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="16">
+        <v>46234</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>211</v>
+      </c>
       <c r="G8" s="21"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
@@ -2003,15 +2025,25 @@
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="10"/>
+      <c r="B9" s="32">
+        <v>46234</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>212</v>
+      </c>
       <c r="G9" s="14"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
@@ -2026,14 +2058,22 @@
       <c r="R9" s="30"/>
       <c r="S9" s="30"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="B10" s="16">
+        <v>46234</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>210</v>
+      </c>
       <c r="F10" s="12"/>
       <c r="G10" s="21"/>
       <c r="H10" s="19"/>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64809470-729F-4D82-BD22-3175A6131717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE0F560B-9552-4320-A7A6-0C5BAD87BD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="21276" windowHeight="12948" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="215">
   <si>
     <t>sarja</t>
   </si>
@@ -762,6 +762,12 @@
   <si>
     <t>Paajanen/
 Puolakka</t>
+  </si>
+  <si>
+    <t>8-21,22-24</t>
+  </si>
+  <si>
+    <t>17-21,21-16,9-15</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1566,7 @@
       </c>
       <c r="C8" s="12">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D8" s="12">
         <f>JNCT_2026!Q3</f>
@@ -1571,7 +1577,7 @@
       </c>
       <c r="F8" s="12">
         <f>JNCT_2026!S2</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G8" s="12">
         <f>JNCT_2026!Q3</f>
@@ -1579,15 +1585,15 @@
       </c>
       <c r="H8" s="12">
         <f>JNCT_2026!R3</f>
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I8" s="12">
         <f>JNCT_2026!Q4</f>
-        <v>152</v>
+        <v>260</v>
       </c>
       <c r="J8" s="12">
         <f>JNCT_2026!R4</f>
-        <v>252</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1597,7 +1603,7 @@
       <c r="B9" s="33"/>
       <c r="C9" s="33">
         <f>SUM(C2:C8)</f>
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D9" s="33">
         <f t="shared" ref="D9:J9" si="1">SUM(D2:D8)</f>
@@ -1609,7 +1615,7 @@
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G9" s="33">
         <f t="shared" si="1"/>
@@ -1617,15 +1623,15 @@
       </c>
       <c r="H9" s="33">
         <f t="shared" si="1"/>
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="I9" s="33">
         <f t="shared" si="1"/>
-        <v>2419</v>
+        <v>2527</v>
       </c>
       <c r="J9" s="33">
         <f t="shared" si="1"/>
-        <v>2751</v>
+        <v>2890</v>
       </c>
     </row>
   </sheetData>
@@ -1641,7 +1647,9 @@
   <cols>
     <col min="1" max="3" width="10.77734375" customWidth="1"/>
     <col min="4" max="6" width="14.77734375" customWidth="1"/>
-    <col min="7" max="19" width="10.77734375" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="9" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1744,11 +1752,11 @@
       </c>
       <c r="R2" s="12">
         <f>SUM(L2:L12)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S2" s="12">
         <f>SUM(Q2:R2)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1798,11 +1806,11 @@
       </c>
       <c r="R3" s="30">
         <f>SUM(K2:K12)*1+SUM(L2:L12)*3</f>
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="S3" s="30">
         <f>SUM(Q3:R3)</f>
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1850,15 +1858,15 @@
       </c>
       <c r="Q4" s="12">
         <f>SUM(M2:M12)</f>
-        <v>152</v>
+        <v>260</v>
       </c>
       <c r="R4" s="12">
         <f>SUM(N2:N12)</f>
-        <v>252</v>
+        <v>391</v>
       </c>
       <c r="S4" s="12">
         <f>SUM(Q4:R4)</f>
-        <v>404</v>
+        <v>651</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -2011,14 +2019,24 @@
       <c r="F8" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="G8" s="21"/>
-      <c r="H8" s="19"/>
+      <c r="G8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>213</v>
+      </c>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
       <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
+      <c r="L8" s="19">
+        <v>1</v>
+      </c>
+      <c r="M8" s="19">
+        <v>30</v>
+      </c>
+      <c r="N8" s="19">
+        <v>45</v>
+      </c>
       <c r="O8" s="19"/>
       <c r="P8" s="18"/>
       <c r="Q8" s="12"/>
@@ -2044,14 +2062,24 @@
       <c r="F9" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="10"/>
+      <c r="G9" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
+      <c r="L9" s="10">
+        <v>1</v>
+      </c>
+      <c r="M9" s="10">
+        <v>31</v>
+      </c>
+      <c r="N9" s="10">
+        <v>42</v>
+      </c>
       <c r="O9" s="10"/>
       <c r="P9" s="29"/>
       <c r="Q9" s="30"/>
@@ -2074,15 +2102,27 @@
       <c r="E10" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="19"/>
+      <c r="F10" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>214</v>
+      </c>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
       <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
+      <c r="L10" s="19">
+        <v>1</v>
+      </c>
+      <c r="M10" s="19">
+        <v>47</v>
+      </c>
+      <c r="N10" s="19">
+        <v>52</v>
+      </c>
       <c r="O10" s="19"/>
       <c r="P10" s="18"/>
       <c r="Q10" s="12"/>
@@ -2244,15 +2284,15 @@
       </c>
       <c r="L23">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <f t="shared" si="0"/>
-        <v>152</v>
+        <v>260</v>
       </c>
       <c r="N23">
         <f t="shared" si="0"/>
-        <v>252</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE0F560B-9552-4320-A7A6-0C5BAD87BD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D969DE-8A5E-48EB-BEE1-1F3D8685E57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="21276" windowHeight="12948" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="21276" windowHeight="12948" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="219">
   <si>
     <t>sarja</t>
   </si>
@@ -768,6 +768,20 @@
   </si>
   <si>
     <t>17-21,21-16,9-15</t>
+  </si>
+  <si>
+    <t>Karkkila</t>
+  </si>
+  <si>
+    <t>Katoperä/
+Laukkanen</t>
+  </si>
+  <si>
+    <t>Punnonen/
+Häkkinen</t>
+  </si>
+  <si>
+    <t>Heikkilä/Niemi</t>
   </si>
 </sst>
 </file>
@@ -2129,14 +2143,22 @@
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
+      <c r="B11" s="32">
+        <v>46243</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>210</v>
+      </c>
       <c r="F11" s="10"/>
       <c r="G11" s="14"/>
       <c r="H11" s="10"/>
@@ -2152,14 +2174,22 @@
       <c r="R11" s="30"/>
       <c r="S11" s="30"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="B12" s="16">
+        <v>46243</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>210</v>
+      </c>
       <c r="F12" s="12"/>
       <c r="G12" s="21"/>
       <c r="H12" s="19"/>
@@ -2175,14 +2205,22 @@
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
+      <c r="B13" s="32">
+        <v>46243</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>210</v>
+      </c>
       <c r="F13" s="10"/>
       <c r="G13" s="14"/>
       <c r="H13" s="10"/>
@@ -2915,7 +2953,7 @@
         <v>46</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>41</v>
+        <v>195</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>178</v>
@@ -2959,7 +2997,7 @@
         <v>46</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>41</v>
+        <v>195</v>
       </c>
       <c r="E13" s="30" t="s">
         <v>178</v>
@@ -3003,7 +3041,7 @@
         <v>46</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>41</v>
+        <v>195</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>178</v>
@@ -3047,7 +3085,7 @@
         <v>46</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>41</v>
+        <v>195</v>
       </c>
       <c r="E15" s="30" t="s">
         <v>178</v>
@@ -3091,7 +3129,7 @@
         <v>46</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>41</v>
+        <v>195</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>178</v>
@@ -3117,32 +3155,146 @@
       <c r="N16" s="12">
         <v>42</v>
       </c>
-      <c r="O16" s="12"/>
+      <c r="O16" s="12">
+        <v>2</v>
+      </c>
       <c r="P16" s="18"/>
       <c r="Q16" s="12"/>
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
       <c r="T16" s="12"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="9"/>
-      <c r="E17" s="3"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="9"/>
-      <c r="E18" s="3"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="9"/>
-      <c r="E19" s="3"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="9"/>
-      <c r="E20" s="3"/>
-      <c r="G20" s="4"/>
+    <row r="17" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="32">
+        <v>46241</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="G17" s="36"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="30"/>
+      <c r="S17" s="30"/>
+      <c r="T17" s="30"/>
+    </row>
+    <row r="18" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="16">
+        <v>46241</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="G18" s="17"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+    </row>
+    <row r="19" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="32">
+        <v>46241</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" s="30"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="30"/>
+    </row>
+    <row r="20" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" s="16">
+        <v>46241</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F20" s="12"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D969DE-8A5E-48EB-BEE1-1F3D8685E57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB918251-748E-48AC-BE30-7F0D7BD3BDAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="21276" windowHeight="12948" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="21276" windowHeight="12948" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="222">
   <si>
     <t>sarja</t>
   </si>
@@ -782,6 +782,16 @@
   </si>
   <si>
     <t>Heikkilä/Niemi</t>
+  </si>
+  <si>
+    <t>21-19,19-21,6-15</t>
+  </si>
+  <si>
+    <t>13-21,14-21</t>
+  </si>
+  <si>
+    <t>Mattila/
+Rajala</t>
   </si>
 </sst>
 </file>
@@ -1540,7 +1550,7 @@
       </c>
       <c r="C7" s="10">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D7" s="10">
         <f>U18_2026!Q2</f>
@@ -1552,7 +1562,7 @@
       </c>
       <c r="F7" s="10">
         <f>U18_2026!T2</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G7" s="10">
         <f>U18_2026!Q3</f>
@@ -1560,7 +1570,7 @@
       </c>
       <c r="H7" s="10">
         <f>U18_2026!S3</f>
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I7" s="10">
         <f>U18_2026!Q4</f>
@@ -1617,7 +1627,7 @@
       <c r="B9" s="33"/>
       <c r="C9" s="33">
         <f>SUM(C2:C8)</f>
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D9" s="33">
         <f t="shared" ref="D9:J9" si="1">SUM(D2:D8)</f>
@@ -1629,7 +1639,7 @@
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G9" s="33">
         <f t="shared" si="1"/>
@@ -1637,7 +1647,7 @@
       </c>
       <c r="H9" s="33">
         <f t="shared" si="1"/>
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="I9" s="33">
         <f t="shared" si="1"/>
@@ -2458,11 +2468,11 @@
       </c>
       <c r="S2" s="12">
         <f>SUM(L2:L20)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T2" s="12">
         <f t="shared" ref="T2:T9" si="0">SUM(Q2:S2)</f>
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -2513,11 +2523,11 @@
       <c r="R3" s="30"/>
       <c r="S3" s="30">
         <f>SUM(K2:K20)*1+SUM(L2:L20)*3</f>
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="T3" s="30">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -3183,14 +3193,24 @@
       <c r="F17" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="G17" s="36"/>
-      <c r="H17" s="35"/>
+      <c r="G17" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="I17" s="35"/>
       <c r="J17" s="35"/>
       <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
+      <c r="L17" s="35">
+        <v>1</v>
+      </c>
+      <c r="M17" s="35">
+        <v>46</v>
+      </c>
+      <c r="N17" s="35">
+        <v>55</v>
+      </c>
       <c r="O17" s="35"/>
       <c r="P17" s="29"/>
       <c r="Q17" s="30"/>
@@ -3217,14 +3237,24 @@
       <c r="F18" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="G18" s="17"/>
-      <c r="H18" s="12"/>
+      <c r="G18" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>220</v>
+      </c>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
+      <c r="L18" s="12">
+        <v>1</v>
+      </c>
+      <c r="M18" s="12">
+        <v>27</v>
+      </c>
+      <c r="N18" s="12">
+        <v>42</v>
+      </c>
       <c r="O18" s="12"/>
       <c r="P18" s="18"/>
       <c r="Q18" s="12"/>
@@ -3248,15 +3278,27 @@
       <c r="E19" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="F19" s="30"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="35"/>
+      <c r="F19" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="G19" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>105</v>
+      </c>
       <c r="I19" s="35"/>
       <c r="J19" s="35"/>
       <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
+      <c r="L19" s="35">
+        <v>1</v>
+      </c>
+      <c r="M19" s="35">
+        <v>21</v>
+      </c>
+      <c r="N19" s="35">
+        <v>42</v>
+      </c>
       <c r="O19" s="35"/>
       <c r="P19" s="29"/>
       <c r="Q19" s="30"/>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB918251-748E-48AC-BE30-7F0D7BD3BDAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C795C6-97CA-4356-87C2-C40AC208CF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="21276" windowHeight="12948" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3299,7 +3299,9 @@
       <c r="N19" s="35">
         <v>42</v>
       </c>
-      <c r="O19" s="35"/>
+      <c r="O19" s="35">
+        <v>9</v>
+      </c>
       <c r="P19" s="29"/>
       <c r="Q19" s="30"/>
       <c r="R19" s="30"/>

--- a/beachvolley.xlsx
+++ b/beachvolley.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C795C6-97CA-4356-87C2-C40AC208CF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBBB641-D12D-4970-84BD-7EF4558D882E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="21276" windowHeight="12948" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="21276" windowHeight="12948" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="225">
   <si>
     <t>sarja</t>
   </si>
@@ -792,6 +792,18 @@
   <si>
     <t>Mattila/
 Rajala</t>
+  </si>
+  <si>
+    <t>Kanervo/
+Kyytsönen</t>
+  </si>
+  <si>
+    <t>Konopko/
+Tuomola</t>
+  </si>
+  <si>
+    <t>Elomaa/
+Koski</t>
   </si>
 </sst>
 </file>
@@ -2169,7 +2181,9 @@
       <c r="E11" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="F11" s="10"/>
+      <c r="F11" s="10" t="s">
+        <v>222</v>
+      </c>
       <c r="G11" s="14"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
@@ -2200,7 +2214,9 @@
       <c r="E12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="F12" s="12"/>
+      <c r="F12" s="12" t="s">
+        <v>223</v>
+      </c>
       <c r="G12" s="21"/>
       <c r="H12" s="19"/>
       <c r="I12" s="19"/>
@@ -2231,7 +2247,9 @@
       <c r="E13" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="F13" s="10"/>
+      <c r="F13" s="10" t="s">
+        <v>224</v>
+      </c>
       <c r="G13" s="14"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
@@ -2246,14 +2264,22 @@
       <c r="R13" s="30"/>
       <c r="S13" s="30"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
+      <c r="B14" s="16">
+        <v>46243</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>210</v>
+      </c>
       <c r="F14" s="12"/>
       <c r="G14" s="21"/>
       <c r="H14" s="19"/>
@@ -2293,31 +2319,67 @@
       <c r="S15" s="30"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="9"/>
-      <c r="E16" s="3"/>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B17" s="9"/>
-      <c r="E17" s="3"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="32"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="30"/>
+      <c r="S17" s="30"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B18" s="9"/>
       <c r="E18" s="3"/>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B19" s="9"/>
       <c r="E19" s="3"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B20" s="9"/>
       <c r="E20" s="3"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="I23">
         <f t="shared" ref="I23:N23" si="0">SUM(I2:I22)</f>
         <v>0</v>
@@ -3308,7 +3370,7 @@
       <c r="S19" s="30"/>
       <c r="T19" s="30"/>
     </row>
-    <row r="20" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>99</v>
       </c>
@@ -3321,9 +3383,7 @@
       <c r="D20" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>216</v>
-      </c>
+      <c r="E20" s="12"/>
       <c r="F20" s="12"/>
       <c r="G20" s="17"/>
       <c r="H20" s="12"/>
